--- a/Models/Молоко/results/Молоко - Результаты прогнозов Prophet.xlsx
+++ b/Models/Молоко/results/Молоко - Результаты прогнозов Prophet.xlsx
@@ -478,31 +478,31 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>4194.15</v>
+        <v>4493.28</v>
       </c>
       <c r="E2" t="n">
-        <v>4167.78</v>
+        <v>4465.77</v>
       </c>
       <c r="F2" t="n">
-        <v>31.84</v>
+        <v>21.45</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>[7214.59, 7751.32, 12624.56]</t>
+          <t>[18828.81, 18141.55, 13314.04]</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>[10829.7, 11876.6, 17387.5]</t>
+          <t>[22673.0, 22635.3, 18373.4]</t>
         </is>
       </c>
     </row>
@@ -514,31 +514,31 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>4073.55</v>
+        <v>4383.14</v>
       </c>
       <c r="E3" t="n">
-        <v>4069.08</v>
+        <v>4374.8</v>
       </c>
       <c r="F3" t="n">
-        <v>25.66</v>
+        <v>23.6</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>[8033.05, 13333.75, 15911.15]</t>
+          <t>[18553.01, 13639.26, 11641.92]</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>[11876.6, 17387.5, 20221.1]</t>
+          <t>[22635.3, 18373.4, 15949.9]</t>
         </is>
       </c>
     </row>
@@ -550,31 +550,31 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>3613.57</v>
+        <v>4203.73</v>
       </c>
       <c r="E4" t="n">
-        <v>3577.68</v>
+        <v>4185.63</v>
       </c>
       <c r="F4" t="n">
-        <v>17.41</v>
+        <v>24.82</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>[14239.76, 16926.94, 19767.66]</t>
+          <t>[13723.87, 11738.69, 12545.24]</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>[17387.5, 20221.1, 24058.8]</t>
+          <t>[18373.4, 15949.9, 16241.4]</t>
         </is>
       </c>
     </row>
@@ -586,31 +586,31 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>3780.85</v>
+        <v>4022.31</v>
       </c>
       <c r="E5" t="n">
-        <v>3743.93</v>
+        <v>3984.93</v>
       </c>
       <c r="F5" t="n">
-        <v>15.47</v>
+        <v>28.79</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>[17190.79, 20144.61, 23989.73]</t>
+          <t>[12010.84, 12902.47, 6701.32]</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>[20221.1, 24058.8, 28277.0]</t>
+          <t>[15949.9, 16241.4, 11378.1]</t>
         </is>
       </c>
     </row>
@@ -622,31 +622,31 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>4496.18</v>
+        <v>3775.38</v>
       </c>
       <c r="E6" t="n">
-        <v>4450.01</v>
+        <v>3727.69</v>
       </c>
       <c r="F6" t="n">
-        <v>17.02</v>
+        <v>29.5</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>[20206.47, 24121.17, 20925.82]</t>
+          <t>[13239.95, 6911.61, 8360.05]</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>[24058.8, 28277.0, 26267.7]</t>
+          <t>[16241.4, 11378.1, 12075.2]</t>
         </is>
       </c>
     </row>
@@ -658,31 +658,31 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>4326.51</v>
+        <v>3918.85</v>
       </c>
       <c r="E7" t="n">
-        <v>4299.15</v>
+        <v>3890.98</v>
       </c>
       <c r="F7" t="n">
-        <v>16.94</v>
+        <v>28.95</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>[24636.23, 21469.12, 18214.9]</t>
+          <t>[7263.45, 8833.66, 13796.95]</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>[28277.0, 26267.7, 22673.0]</t>
+          <t>[11378.1, 12075.2, 18113.7]</t>
         </is>
       </c>
     </row>
@@ -694,31 +694,31 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>4553.78</v>
+        <v>3196.56</v>
       </c>
       <c r="E8" t="n">
-        <v>4546.07</v>
+        <v>3179.78</v>
       </c>
       <c r="F8" t="n">
-        <v>19.15</v>
+        <v>19.57</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>[21713.86, 18455.2, 17768.73]</t>
+          <t>[9173.98, 14474.81, 17536.87]</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>[26267.7, 22673.0, 22635.3]</t>
+          <t>[12075.2, 18113.7, 20536.1]</t>
         </is>
       </c>
     </row>
@@ -730,31 +730,31 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>4493.28</v>
+        <v>1845.29</v>
       </c>
       <c r="E9" t="n">
-        <v>4465.77</v>
+        <v>1782.39</v>
       </c>
       <c r="F9" t="n">
-        <v>21.45</v>
+        <v>8.81</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>[18828.81, 18141.55, 13314.04]</t>
+          <t>[15656.69, 19059.97, 23491.68]</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>[22673.0, 22635.3, 18373.4]</t>
+          <t>[18113.7, 20536.1, 24905.7]</t>
         </is>
       </c>
     </row>
@@ -766,31 +766,31 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>4383.14</v>
+        <v>763.79</v>
       </c>
       <c r="E10" t="n">
-        <v>4374.8</v>
+        <v>601.14</v>
       </c>
       <c r="F10" t="n">
-        <v>23.6</v>
+        <v>2.22</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>[18553.01, 13639.26, 11641.92]</t>
+          <t>[20581.37, 25466.55, 29688.9]</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>[22635.3, 18373.4, 15949.9]</t>
+          <t>[20536.1, 24905.7, 28491.6]</t>
         </is>
       </c>
     </row>
@@ -802,31 +802,31 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>4203.73</v>
+        <v>2158.54</v>
       </c>
       <c r="E11" t="n">
-        <v>4185.63</v>
+        <v>2100.5</v>
       </c>
       <c r="F11" t="n">
-        <v>24.82</v>
+        <v>7.99</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>[13723.87, 11738.69, 12545.24]</t>
+          <t>[26331.84, 30757.03, 27989.84]</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>[18373.4, 15949.9, 16241.4]</t>
+          <t>[24905.7, 28491.6, 25379.9]</t>
         </is>
       </c>
     </row>
@@ -838,31 +838,31 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1689.42</v>
+        <v>4262.61</v>
       </c>
       <c r="E12" t="n">
-        <v>1569.79</v>
+        <v>4246.81</v>
       </c>
       <c r="F12" t="n">
-        <v>21.69</v>
+        <v>24.47</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>[2697.53, 5299.24, 12721.55]</t>
+          <t>[14951.13, 14056.58, 10672.06]</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>[3531.8, 7660.0, 14235.9]</t>
+          <t>[19708.6, 18126.4, 14585.2]</t>
         </is>
       </c>
     </row>
@@ -874,31 +874,31 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1792.32</v>
+        <v>4023.69</v>
       </c>
       <c r="E13" t="n">
-        <v>1730.8</v>
+        <v>4005.53</v>
       </c>
       <c r="F13" t="n">
-        <v>17.51</v>
+        <v>27.82</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>[5294.04, 12972.91, 10683.75]</t>
+          <t>[14334.85, 10902.09, 7637.58]</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>[7660.0, 14235.9, 12247.2]</t>
+          <t>[18126.4, 14585.2, 12179.5]</t>
         </is>
       </c>
     </row>
@@ -910,31 +910,31 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>997.74</v>
+        <v>3761.36</v>
       </c>
       <c r="E14" t="n">
-        <v>913.6900000000001</v>
+        <v>3737.87</v>
       </c>
       <c r="F14" t="n">
-        <v>6.59</v>
+        <v>30.27</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>[13813.55, 11332.64, 13620.75]</t>
+          <t>[11145.74, 7848.1, 7431.06]</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>[14235.9, 12247.2, 15024.9]</t>
+          <t>[14585.2, 12179.5, 10873.8]</t>
         </is>
       </c>
     </row>
@@ -946,31 +946,31 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1470.74</v>
+        <v>3198.98</v>
       </c>
       <c r="E15" t="n">
-        <v>1438.71</v>
+        <v>3001.91</v>
       </c>
       <c r="F15" t="n">
-        <v>8.41</v>
+        <v>35.52</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>[11204.52, 13537.02, 24438.52]</t>
+          <t>[7988.16, 7588.0, 2116.52]</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>[12247.2, 15024.9, 26224.1]</t>
+          <t>[12179.5, 10873.8, 3645.1]</t>
         </is>
       </c>
     </row>
@@ -982,31 +982,31 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>2988.53</v>
+        <v>2104.22</v>
       </c>
       <c r="E16" t="n">
-        <v>2579.87</v>
+        <v>1947.6</v>
       </c>
       <c r="F16" t="n">
-        <v>12.37</v>
+        <v>28.29</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>[13533.29, 24689.17, 17398.13]</t>
+          <t>[7801.7, 2200.26, 6477.05]</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>[15024.9, 26224.1, 22111.2]</t>
+          <t>[10873.8, 3645.1, 7802.9]</t>
         </is>
       </c>
     </row>
@@ -1018,31 +1018,31 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3979.04</v>
+        <v>1928.69</v>
       </c>
       <c r="E17" t="n">
-        <v>3620.59</v>
+        <v>1796.56</v>
       </c>
       <c r="F17" t="n">
-        <v>16.99</v>
+        <v>24.34</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>[24918.08, 17594.44, 14669.6]</t>
+          <t>[2240.6, 6599.65, 11802.27]</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>[26224.1, 22111.2, 19708.6]</t>
+          <t>[3645.1, 7802.9, 14584.2]</t>
         </is>
       </c>
     </row>
@@ -1054,31 +1054,31 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>4798.53</v>
+        <v>1851.72</v>
       </c>
       <c r="E18" t="n">
-        <v>4789.5</v>
+        <v>1762.17</v>
       </c>
       <c r="F18" t="n">
-        <v>24.1</v>
+        <v>14.77</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>[17413.05, 14521.81, 13642.84]</t>
+          <t>[6839.22, 12337.47, 10474.91]</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>[22111.2, 19708.6, 18126.4]</t>
+          <t>[7802.9, 14584.2, 12551.0]</t>
         </is>
       </c>
     </row>
@@ -1090,31 +1090,31 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>4262.61</v>
+        <v>1912.88</v>
       </c>
       <c r="E19" t="n">
-        <v>4246.81</v>
+        <v>1905.26</v>
       </c>
       <c r="F19" t="n">
-        <v>24.47</v>
+        <v>13.58</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>[14951.13, 14056.58, 10672.06]</t>
+          <t>[12486.79, 10615.49, 13713.34]</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>[19708.6, 18126.4, 14585.2]</t>
+          <t>[14584.2, 12551.0, 15396.2]</t>
         </is>
       </c>
     </row>
@@ -1126,31 +1126,31 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>4023.69</v>
+        <v>2536.92</v>
       </c>
       <c r="E20" t="n">
-        <v>4005.53</v>
+        <v>2291.16</v>
       </c>
       <c r="F20" t="n">
-        <v>27.82</v>
+        <v>12.19</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>[14334.85, 10902.09, 7637.58]</t>
+          <t>[10854.07, 14038.77, 23018.98]</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>[18126.4, 14585.2, 12179.5]</t>
+          <t>[12551.0, 15396.2, 26838.1]</t>
         </is>
       </c>
     </row>
@@ -1162,31 +1162,31 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>3761.36</v>
+        <v>2743.26</v>
       </c>
       <c r="E21" t="n">
-        <v>3737.87</v>
+        <v>2374.76</v>
       </c>
       <c r="F21" t="n">
-        <v>30.27</v>
+        <v>10.37</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>[11145.74, 7848.1, 7431.06]</t>
+          <t>[14775.75, 24307.88, 18531.51]</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>[14585.2, 12179.5, 10873.8]</t>
+          <t>[15396.2, 26838.1, 22505.1]</t>
         </is>
       </c>
     </row>
@@ -1198,31 +1198,31 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>6369.43</v>
+        <v>15706.35</v>
       </c>
       <c r="E22" t="n">
-        <v>6310.07</v>
+        <v>15627.06</v>
       </c>
       <c r="F22" t="n">
-        <v>36.01</v>
+        <v>49.26</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>[11404.96, 10181.65, 11809.79]</t>
+          <t>[16633.47, 19126.39, 12921.44]</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>[18455.6, 15274.2, 18596.8]</t>
+          <t>[32883.5, 32588.5, 30090.5]</t>
         </is>
       </c>
     </row>
@@ -1234,31 +1234,31 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>5538.26</v>
+        <v>12793.12</v>
       </c>
       <c r="E23" t="n">
-        <v>5505.7</v>
+        <v>12338.29</v>
       </c>
       <c r="F23" t="n">
-        <v>31.09</v>
+        <v>43.24</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>[10616.54, 12666.98, 13257.29]</t>
+          <t>[20110.94, 13682.86, 13901.14]</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>[15274.2, 18596.8, 19186.9]</t>
+          <t>[32588.5, 30090.5, 22030.8]</t>
         </is>
       </c>
     </row>
@@ -1270,31 +1270,31 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>5250.68</v>
+        <v>10889.42</v>
       </c>
       <c r="E24" t="n">
-        <v>5236.56</v>
+        <v>10060.42</v>
       </c>
       <c r="F24" t="n">
-        <v>26.1</v>
+        <v>43.3</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>[13618.92, 14235.61, 16680.79]</t>
+          <t>[14163.85, 14411.81, 9016.38]</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>[18596.8, 19186.9, 22461.3]</t>
+          <t>[30090.5, 22030.8, 15652.0]</t>
         </is>
       </c>
     </row>
@@ -1306,31 +1306,31 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>9570.049999999999</v>
+        <v>5937.77</v>
       </c>
       <c r="E25" t="n">
-        <v>8302.08</v>
+        <v>5926.04</v>
       </c>
       <c r="F25" t="n">
-        <v>31.19</v>
+        <v>32.07</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>[14576.49, 17188.9, 17585.08]</t>
+          <t>[16092.71, 10188.74, 12192.12]</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>[19186.9, 22461.3, 32608.5]</t>
+          <t>[22030.8, 15652.0, 18568.9]</t>
         </is>
       </c>
     </row>
@@ -1342,31 +1342,31 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>12119.59</v>
+        <v>4713.4</v>
       </c>
       <c r="E26" t="n">
-        <v>11222.52</v>
+        <v>4706</v>
       </c>
       <c r="F26" t="n">
-        <v>38.05</v>
+        <v>27.93</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>[17709.78, 18212.99, 15203.78]</t>
+          <t>[11291.08, 13566.98, 11641.24]</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>[22461.3, 32608.5, 29724.3]</t>
+          <t>[15652.0, 18568.9, 16396.4]</t>
         </is>
       </c>
     </row>
@@ -1378,31 +1378,31 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>15406.3</v>
+        <v>3243.94</v>
       </c>
       <c r="E27" t="n">
-        <v>15299.15</v>
+        <v>3236.93</v>
       </c>
       <c r="F27" t="n">
-        <v>48.16</v>
+        <v>17.8</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>[18683.55, 15613.87, 15021.42]</t>
+          <t>[15094.93, 13116.76, 17193.32]</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>[32608.5, 29724.3, 32883.5]</t>
+          <t>[18568.9, 16396.4, 20150.5]</t>
         </is>
       </c>
     </row>
@@ -1414,31 +1414,31 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>15062.64</v>
+        <v>2178.85</v>
       </c>
       <c r="E28" t="n">
-        <v>14981.83</v>
+        <v>1937.17</v>
       </c>
       <c r="F28" t="n">
-        <v>47.13</v>
+        <v>10.71</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>[16369.54, 15801.03, 18080.26]</t>
+          <t>[13530.49, 17758.36, 19263.04]</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>[29724.3, 32883.5, 32588.5]</t>
+          <t>[16396.4, 20150.5, 19816.5]</t>
         </is>
       </c>
     </row>
@@ -1450,31 +1450,31 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>15706.35</v>
+        <v>1420.42</v>
       </c>
       <c r="E29" t="n">
-        <v>15627.06</v>
+        <v>1333.73</v>
       </c>
       <c r="F29" t="n">
-        <v>49.26</v>
+        <v>6.21</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>[16633.47, 19126.39, 12921.44]</t>
+          <t>[18911.05, 20604.5, 25186.73]</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>[32883.5, 32588.5, 30090.5]</t>
+          <t>[20150.5, 19816.5, 23213.0]</t>
         </is>
       </c>
     </row>
@@ -1486,31 +1486,31 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>12793.12</v>
+        <v>3107.55</v>
       </c>
       <c r="E30" t="n">
-        <v>12338.29</v>
+        <v>3001.3</v>
       </c>
       <c r="F30" t="n">
-        <v>43.24</v>
+        <v>12.48</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>[20110.94, 13682.86, 13901.14]</t>
+          <t>[22263.26, 27353.52, 30843.87]</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>[32588.5, 30090.5, 22030.8]</t>
+          <t>[19816.5, 23213.0, 33260.5]</t>
         </is>
       </c>
     </row>
@@ -1522,31 +1522,31 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>10889.42</v>
+        <v>3607.33</v>
       </c>
       <c r="E31" t="n">
-        <v>10060.42</v>
+        <v>3476.07</v>
       </c>
       <c r="F31" t="n">
-        <v>43.3</v>
+        <v>12.57</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>[14163.85, 14411.81, 9016.38]</t>
+          <t>[27563.54, 31127.85, 27493.89]</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>[30090.5, 22030.8, 15652.0]</t>
+          <t>[23213.0, 33260.5, 31438.9]</t>
         </is>
       </c>
     </row>
@@ -1558,31 +1558,31 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>316.51</v>
+        <v>956.47</v>
       </c>
       <c r="E32" t="n">
-        <v>302.99</v>
+        <v>901.05</v>
       </c>
       <c r="F32" t="n">
-        <v>22.34</v>
+        <v>32.95</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>[853.58, 918.29, 1328.06]</t>
+          <t>[2124.13, 2156.42, 1052.9]</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>[1105.5, 1143.8, 1759.6]</t>
+          <t>[3263.7, 3272.5, 1500.4]</t>
         </is>
       </c>
     </row>
@@ -1594,31 +1594,31 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>364.43</v>
+        <v>763.4299999999999</v>
       </c>
       <c r="E33" t="n">
-        <v>341.05</v>
+        <v>719.87</v>
       </c>
       <c r="F33" t="n">
-        <v>17.94</v>
+        <v>30.17</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>[963.57, 1411.18, 2211.58]</t>
+          <t>[2245.42, 1095.81, 1534.76]</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>[1143.8, 1759.6, 2706.1]</t>
+          <t>[3272.5, 1500.4, 2262.7]</t>
         </is>
       </c>
     </row>
@@ -1630,31 +1630,31 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>712.17</v>
+        <v>818.13</v>
       </c>
       <c r="E34" t="n">
-        <v>634.9</v>
+        <v>745.71</v>
       </c>
       <c r="F34" t="n">
-        <v>19.48</v>
+        <v>32.9</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>[1422.08, 2222.19, 3985.73]</t>
+          <t>[1126.73, 1588.02, 1513.53]</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>[1759.6, 2706.1, 5069.0]</t>
+          <t>[1500.4, 2262.7, 2702.3]</t>
         </is>
       </c>
     </row>
@@ -1666,31 +1666,31 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>939.28</v>
+        <v>786.27</v>
       </c>
       <c r="E35" t="n">
-        <v>879.99</v>
+        <v>710.95</v>
       </c>
       <c r="F35" t="n">
-        <v>22.69</v>
+        <v>33.87</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>[2272.4, 4077.23, 2525.1]</t>
+          <t>[1617.02, 1551.34, 766.38]</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>[2706.1, 5069.0, 3739.6]</t>
+          <t>[2262.7, 2702.3, 1102.6]</t>
         </is>
       </c>
     </row>
@@ -1702,31 +1702,31 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>1077.19</v>
+        <v>684.5599999999999</v>
       </c>
       <c r="E36" t="n">
-        <v>1070.38</v>
+        <v>573.77</v>
       </c>
       <c r="F36" t="n">
-        <v>28.96</v>
+        <v>31.95</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>[4022.44, 2510.69, 1869.02]</t>
+          <t>[1600.49, 793.54, 836.98]</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>[5069.0, 3739.6, 2804.7]</t>
+          <t>[2702.3, 1102.6, 1147.4]</t>
         </is>
       </c>
     </row>
@@ -1738,31 +1738,31 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>1133.66</v>
+        <v>362.62</v>
       </c>
       <c r="E37" t="n">
-        <v>1120.69</v>
+        <v>351.09</v>
       </c>
       <c r="F37" t="n">
-        <v>34.3</v>
+        <v>25.96</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>[2564.42, 1915.33, 1966.18]</t>
+          <t>[812.31, 863.72, 1307.89]</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>[3739.6, 2804.7, 3263.7]</t>
+          <t>[1102.6, 1147.4, 1787.2]</t>
         </is>
       </c>
     </row>
@@ -1774,31 +1774,31 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>1075.73</v>
+        <v>478.67</v>
       </c>
       <c r="E38" t="n">
-        <v>1060.1</v>
+        <v>449.6</v>
       </c>
       <c r="F38" t="n">
-        <v>33.79</v>
+        <v>23.26</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>[2002.64, 2063.6, 2094.35]</t>
+          <t>[895.07, 1345.22, 2185.4]</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>[2804.7, 3263.7, 3272.5]</t>
+          <t>[1147.4, 1787.2, 2839.9]</t>
         </is>
       </c>
     </row>
@@ -1810,31 +1810,31 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>956.47</v>
+        <v>931.51</v>
       </c>
       <c r="E39" t="n">
-        <v>901.05</v>
+        <v>813.14</v>
       </c>
       <c r="F39" t="n">
-        <v>32.95</v>
+        <v>23.32</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>[2124.13, 2156.42, 1052.9]</t>
+          <t>[1382.81, 2251.85, 3985.7]</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>[3263.7, 3272.5, 1500.4]</t>
+          <t>[1787.2, 2839.9, 5432.7]</t>
         </is>
       </c>
     </row>
@@ -1846,31 +1846,31 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>763.4299999999999</v>
+        <v>995.91</v>
       </c>
       <c r="E40" t="n">
-        <v>719.87</v>
+        <v>931.9299999999999</v>
       </c>
       <c r="F40" t="n">
-        <v>30.17</v>
+        <v>22.16</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>[2245.42, 1095.81, 1534.76]</t>
+          <t>[2403.91, 4276.47, 2828.64]</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>[3272.5, 1500.4, 2262.7]</t>
+          <t>[2839.9, 5432.7, 4032.2]</t>
         </is>
       </c>
     </row>
@@ -1882,31 +1882,31 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>818.13</v>
+        <v>709.29</v>
       </c>
       <c r="E41" t="n">
-        <v>745.71</v>
+        <v>697.86</v>
       </c>
       <c r="F41" t="n">
-        <v>32.9</v>
+        <v>17.43</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>[1126.73, 1588.02, 1513.53]</t>
+          <t>[4747.19, 3173.21, 2438.22]</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>[1500.4, 2262.7, 2702.3]</t>
+          <t>[5432.7, 4032.2, 2987.3]</t>
         </is>
       </c>
     </row>
@@ -1918,31 +1918,31 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>5716.23</v>
+        <v>9257.889999999999</v>
       </c>
       <c r="E42" t="n">
-        <v>5706.81</v>
+        <v>9218.26</v>
       </c>
       <c r="F42" t="n">
-        <v>46.73</v>
+        <v>42.36</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>[5401.32, 5834.88, 8717.87]</t>
+          <t>[15337.55, 13169.98, 9711.5]</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>[10951.0, 11242.4, 14881.1]</t>
+          <t>[25528.8, 21278.6, 19066.4]</t>
         </is>
       </c>
     </row>
@@ -1954,31 +1954,31 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>5760.13</v>
+        <v>9212.84</v>
       </c>
       <c r="E43" t="n">
-        <v>5667.74</v>
+        <v>9136.059999999999</v>
       </c>
       <c r="F43" t="n">
-        <v>38.74</v>
+        <v>46.2</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>[6356.91, 9882.83, 11057.85]</t>
+          <t>[13535.83, 10044.44, 8750.35]</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>[11242.4, 14881.1, 18177.3]</t>
+          <t>[21278.6, 19066.4, 19393.8]</t>
         </is>
       </c>
     </row>
@@ -1990,31 +1990,31 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>5930</v>
+        <v>12663.16</v>
       </c>
       <c r="E44" t="n">
-        <v>5799.03</v>
+        <v>12087.23</v>
       </c>
       <c r="F44" t="n">
-        <v>32.48</v>
+        <v>55.5</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>[10763.12, 11967.53, 12782.55]</t>
+          <t>[10422.74, 9118.67, 8092.12]</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>[14881.1, 18177.3, 19851.9]</t>
+          <t>[19066.4, 19393.8, 25435.0]</t>
         </is>
       </c>
     </row>
@@ -2026,31 +2026,31 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>7699.87</v>
+        <v>11617.39</v>
       </c>
       <c r="E45" t="n">
-        <v>7463.68</v>
+        <v>10866.2</v>
       </c>
       <c r="F45" t="n">
-        <v>34.21</v>
+        <v>56.54</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>[12405.06, 13338.8, 16440.32]</t>
+          <t>[9986.7, 8967.16, 5202.23]</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>[18177.3, 19851.9, 26546.0]</t>
+          <t>[19393.8, 25435.0, 11925.9]</t>
         </is>
       </c>
     </row>
@@ -2062,31 +2062,31 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>9006.799999999999</v>
+        <v>9953.85</v>
       </c>
       <c r="E46" t="n">
-        <v>8741.540000000001</v>
+        <v>8944.290000000001</v>
       </c>
       <c r="F46" t="n">
-        <v>35.35</v>
+        <v>50.85</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>[13979.76, 17311.36, 15549.64]</t>
+          <t>[10313.53, 6067.04, 7456.46]</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>[19851.9, 26546.0, 26667.5]</t>
+          <t>[25435.0, 11925.9, 13309.0]</t>
         </is>
       </c>
     </row>
@@ -2098,31 +2098,31 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>10263.96</v>
+        <v>5137.26</v>
       </c>
       <c r="E47" t="n">
-        <v>10205.92</v>
+        <v>5122.87</v>
       </c>
       <c r="F47" t="n">
-        <v>38.95</v>
+        <v>36.49</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>[17835.33, 16038.5, 14250.72]</t>
+          <t>[6751.19, 8680.49, 12216.09]</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>[26546.0, 26667.5, 25528.8]</t>
+          <t>[11925.9, 13309.0, 17781.5]</t>
         </is>
       </c>
     </row>
@@ -2134,31 +2134,31 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>10025.48</v>
+        <v>4608.28</v>
       </c>
       <c r="E48" t="n">
-        <v>9984.860000000001</v>
+        <v>4564.53</v>
       </c>
       <c r="F48" t="n">
-        <v>40.83</v>
+        <v>26.26</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>[16422.55, 14593.06, 12504.72]</t>
+          <t>[9391.23, 13430.45, 16393.93]</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>[26667.5, 25528.8, 21278.6]</t>
+          <t>[13309.0, 17781.5, 21818.7]</t>
         </is>
       </c>
     </row>
@@ -2170,31 +2170,31 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>9257.889999999999</v>
+        <v>2880.47</v>
       </c>
       <c r="E49" t="n">
-        <v>9218.26</v>
+        <v>2849.03</v>
       </c>
       <c r="F49" t="n">
-        <v>42.36</v>
+        <v>13.68</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>[15337.55, 13169.98, 9711.5]</t>
+          <t>[14970.09, 18432.05, 21830.97]</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>[25528.8, 21278.6, 19066.4]</t>
+          <t>[17781.5, 21818.7, 24180.0]</t>
         </is>
       </c>
     </row>
@@ -2206,31 +2206,31 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>9212.84</v>
+        <v>997.99</v>
       </c>
       <c r="E50" t="n">
-        <v>9136.059999999999</v>
+        <v>710.96</v>
       </c>
       <c r="F50" t="n">
-        <v>46.2</v>
+        <v>3.14</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>[13535.83, 10044.44, 8750.35]</t>
+          <t>[20117.58, 23942.31, 29961.34]</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>[21278.6, 19066.4, 19393.8]</t>
+          <t>[21818.7, 24180.0, 30155.4]</t>
         </is>
       </c>
     </row>
@@ -2242,31 +2242,31 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>12663.16</v>
+        <v>1918.62</v>
       </c>
       <c r="E51" t="n">
-        <v>12087.23</v>
+        <v>1836.46</v>
       </c>
       <c r="F51" t="n">
-        <v>55.5</v>
+        <v>6.61</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>[10422.74, 9118.67, 8092.12]</t>
+          <t>[25388.46, 31897.25, 30805.78]</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>[19066.4, 19393.8, 25435.0]</t>
+          <t>[24180.0, 30155.4, 28246.7]</t>
         </is>
       </c>
     </row>
@@ -2278,31 +2278,31 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>22.68</v>
+        <v>28.43</v>
       </c>
       <c r="E52" t="n">
-        <v>19.04</v>
+        <v>17.95</v>
       </c>
       <c r="F52" t="n">
-        <v>43.05</v>
+        <v>63.76</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>[26.01, 16.0, 13.49]</t>
+          <t>[28.27, 26.9, 77.78]</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>[48.2, 48.3, 16.1]</t>
+          <t>[27.5, 22.9, 28.7]</t>
         </is>
       </c>
     </row>
@@ -2314,31 +2314,31 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>20.14</v>
+        <v>30.5</v>
       </c>
       <c r="E53" t="n">
-        <v>15.74</v>
+        <v>24.45</v>
       </c>
       <c r="F53" t="n">
-        <v>41.1</v>
+        <v>86.93000000000001</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>[16.27, 14.66, 14.85]</t>
+          <t>[27.45, 77.31, 48.39]</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>[48.3, 16.1, 28.6]</t>
+          <t>[22.9, 28.7, 28.2]</t>
         </is>
       </c>
     </row>
@@ -2350,31 +2350,31 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>6.46</v>
+        <v>31.26</v>
       </c>
       <c r="E54" t="n">
-        <v>4.38</v>
+        <v>23.76</v>
       </c>
       <c r="F54" t="n">
-        <v>16.14</v>
+        <v>83.16</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>[15.17, 17.5, 27.99]</t>
+          <t>[78.47, 49.52, 38.79]</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>[16.1, 28.6, 29.1]</t>
+          <t>[28.7, 28.2, 38.6]</t>
         </is>
       </c>
     </row>
@@ -2386,31 +2386,31 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>6.91</v>
+        <v>12.13</v>
       </c>
       <c r="E55" t="n">
-        <v>4.81</v>
+        <v>9.93</v>
       </c>
       <c r="F55" t="n">
-        <v>16.83</v>
+        <v>36.61</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>[16.79, 27.49, 28.3]</t>
+          <t>[46.13, 37.64, 14.0]</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>[28.6, 29.1, 27.3]</t>
+          <t>[28.2, 38.6, 24.9]</t>
         </is>
       </c>
     </row>
@@ -2422,31 +2422,31 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>1.9</v>
+        <v>9.94</v>
       </c>
       <c r="E56" t="n">
-        <v>1.8</v>
+        <v>8.41</v>
       </c>
       <c r="F56" t="n">
-        <v>6.4</v>
+        <v>32.53</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>[27.94, 28.99, 25.83]</t>
+          <t>[37.2, 15.29, 11.47]</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>[29.1, 27.3, 28.4]</t>
+          <t>[38.6, 24.9, 25.7]</t>
         </is>
       </c>
     </row>
@@ -2458,31 +2458,31 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>2.24</v>
+        <v>14.39</v>
       </c>
       <c r="E57" t="n">
-        <v>2.22</v>
+        <v>14.16</v>
       </c>
       <c r="F57" t="n">
-        <v>7.99</v>
+        <v>56.09</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>[29.24, 25.77, 29.59]</t>
+          <t>[14.1, 11.01, 8.1]</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>[27.3, 28.4, 27.5]</t>
+          <t>[24.9, 25.7, 25.1]</t>
         </is>
       </c>
     </row>
@@ -2494,31 +2494,31 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>3.74</v>
+        <v>15.61</v>
       </c>
       <c r="E58" t="n">
-        <v>3.49</v>
+        <v>15.56</v>
       </c>
       <c r="F58" t="n">
-        <v>13.79</v>
+        <v>59.55</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>[24.74, 29.27, 27.94]</t>
+          <t>[11.66, 8.17, 12.09]</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>[28.4, 27.5, 22.9]</t>
+          <t>[25.7, 25.1, 27.8]</t>
         </is>
       </c>
     </row>
@@ -2530,31 +2530,31 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>28.43</v>
+        <v>14.89</v>
       </c>
       <c r="E59" t="n">
-        <v>17.95</v>
+        <v>14.79</v>
       </c>
       <c r="F59" t="n">
-        <v>63.76</v>
+        <v>54.33</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>[28.27, 26.9, 77.78]</t>
+          <t>[8.48, 12.46, 17.41]</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>[27.5, 22.9, 28.7]</t>
+          <t>[25.1, 27.8, 29.8]</t>
         </is>
       </c>
     </row>
@@ -2566,31 +2566,31 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>30.5</v>
+        <v>11.9</v>
       </c>
       <c r="E60" t="n">
-        <v>24.45</v>
+        <v>11.64</v>
       </c>
       <c r="F60" t="n">
-        <v>86.93000000000001</v>
+        <v>40.91</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>[27.45, 77.31, 48.39]</t>
+          <t>[13.12, 18.23, 19.23]</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>[22.9, 28.7, 28.2]</t>
+          <t>[27.8, 29.8, 27.9]</t>
         </is>
       </c>
     </row>
@@ -2602,31 +2602,31 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>31.26</v>
+        <v>9.23</v>
       </c>
       <c r="E61" t="n">
-        <v>23.76</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="F61" t="n">
-        <v>83.16</v>
+        <v>32.24</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>[78.47, 49.52, 38.79]</t>
+          <t>[18.9, 19.86, 18.61]</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>[28.7, 28.2, 38.6]</t>
+          <t>[29.8, 27.9, 27.1]</t>
         </is>
       </c>
     </row>
@@ -2638,31 +2638,31 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>3.43</v>
+        <v>7.7</v>
       </c>
       <c r="E62" t="n">
-        <v>3.33</v>
+        <v>7.47</v>
       </c>
       <c r="F62" t="n">
-        <v>30.61</v>
+        <v>41.43</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>[7.59, 7.49, 7.13]</t>
+          <t>[16.08, 8.72, 7.6]</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>[11.2, 9.7, 11.3]</t>
+          <t>[25.0, 17.4, 12.4]</t>
         </is>
       </c>
     </row>
@@ -2674,31 +2674,31 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>6.26</v>
+        <v>5.8</v>
       </c>
       <c r="E63" t="n">
-        <v>5.21</v>
+        <v>5.03</v>
       </c>
       <c r="F63" t="n">
-        <v>33.42</v>
+        <v>37.64</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>[7.81, 7.59, 10.88]</t>
+          <t>[8.72, 7.61, 4.99]</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>[9.7, 11.3, 20.9]</t>
+          <t>[17.4, 12.4, 6.6]</t>
         </is>
       </c>
     </row>
@@ -2710,31 +2710,31 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>6.76</v>
+        <v>3.05</v>
       </c>
       <c r="E64" t="n">
-        <v>6.17</v>
+        <v>2.73</v>
       </c>
       <c r="F64" t="n">
-        <v>34.94</v>
+        <v>365.14</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>[7.59, 10.87, 15.13]</t>
+          <t>[7.78, 5.11, 2.27]</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>[11.3, 20.9, 19.9]</t>
+          <t>[12.4, 6.6, 0.2]</t>
         </is>
       </c>
     </row>
@@ -2746,31 +2746,31 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>6.44</v>
+        <v>1.49</v>
       </c>
       <c r="E65" t="n">
-        <v>5.64</v>
+        <v>1.35</v>
       </c>
       <c r="F65" t="n">
-        <v>27.99</v>
+        <v>349.54</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>[11.03, 15.37, 15.48]</t>
+          <t>[5.12, 2.24, 7.14]</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>[20.9, 19.9, 18.0]</t>
+          <t>[6.6, 0.2, 6.6]</t>
         </is>
       </c>
     </row>
@@ -2782,31 +2782,31 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>5.27</v>
+        <v>1.45</v>
       </c>
       <c r="E66" t="n">
-        <v>4.79</v>
+        <v>1.36</v>
       </c>
       <c r="F66" t="n">
-        <v>21.85</v>
+        <v>350.73</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>[15.53, 15.64, 17.45]</t>
+          <t>[2.24, 7.45, 7.48]</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>[19.9, 18.0, 25.1]</t>
+          <t>[0.2, 6.6, 6.3]</t>
         </is>
       </c>
     </row>
@@ -2818,31 +2818,31 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>6.92</v>
+        <v>0.26</v>
       </c>
       <c r="E67" t="n">
-        <v>6.26</v>
+        <v>0.21</v>
       </c>
       <c r="F67" t="n">
-        <v>26.12</v>
+        <v>3.33</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>[15.81, 17.64, 15.88]</t>
+          <t>[6.69, 6.72, 6.68]</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>[18.0, 25.1, 25.0]</t>
+          <t>[6.6, 6.3, 6.8]</t>
         </is>
       </c>
     </row>
@@ -2854,31 +2854,31 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>8.279999999999999</v>
+        <v>1.06</v>
       </c>
       <c r="E68" t="n">
-        <v>8.24</v>
+        <v>0.79</v>
       </c>
       <c r="F68" t="n">
-        <v>37.97</v>
+        <v>8.27</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>[17.88, 16.13, 8.76]</t>
+          <t>[6.92, 6.83, 10.08]</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>[25.1, 25.0, 17.4]</t>
+          <t>[6.3, 6.8, 11.8]</t>
         </is>
       </c>
     </row>
@@ -2890,31 +2890,31 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>7.7</v>
+        <v>1.81</v>
       </c>
       <c r="E69" t="n">
-        <v>7.47</v>
+        <v>1.46</v>
       </c>
       <c r="F69" t="n">
-        <v>41.43</v>
+        <v>13.12</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>[16.08, 8.72, 7.6]</t>
+          <t>[6.83, 10.04, 13.4]</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>[25.0, 17.4, 12.4]</t>
+          <t>[6.8, 11.8, 10.8]</t>
         </is>
       </c>
     </row>
@@ -2926,31 +2926,31 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>5.8</v>
+        <v>3.24</v>
       </c>
       <c r="E70" t="n">
-        <v>5.03</v>
+        <v>2.99</v>
       </c>
       <c r="F70" t="n">
-        <v>37.64</v>
+        <v>21.52</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>[8.72, 7.61, 4.99]</t>
+          <t>[10.13, 13.48, 13.47]</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>[17.4, 12.4, 6.6]</t>
+          <t>[11.8, 10.8, 18.1]</t>
         </is>
       </c>
     </row>
@@ -2962,31 +2962,31 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>3.05</v>
+        <v>4.56</v>
       </c>
       <c r="E71" t="n">
-        <v>2.73</v>
+        <v>4.38</v>
       </c>
       <c r="F71" t="n">
-        <v>365.14</v>
+        <v>25.92</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>[7.78, 5.11, 2.27]</t>
+          <t>[13.52, 13.5, 15.59]</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>[12.4, 6.6, 0.2]</t>
+          <t>[10.8, 18.1, 21.4]</t>
         </is>
       </c>
     </row>
@@ -2998,31 +2998,31 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>180.03</v>
+        <v>1171.13</v>
       </c>
       <c r="E72" t="n">
-        <v>136.94</v>
+        <v>1118.68</v>
       </c>
       <c r="F72" t="n">
-        <v>3.23</v>
+        <v>19.02</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>[3531.63, 3983.32, 4933.28]</t>
+          <t>[5703.37, 4425.99, 4399.21]</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>[3430.5, 3968.2, 4638.7]</t>
+          <t>[6371.8, 5602.1, 5910.7]</t>
         </is>
       </c>
     </row>
@@ -3034,31 +3034,31 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>485.86</v>
+        <v>1262.02</v>
       </c>
       <c r="E73" t="n">
-        <v>354.51</v>
+        <v>1254.72</v>
       </c>
       <c r="F73" t="n">
-        <v>6.23</v>
+        <v>22.6</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>[3963.35, 4896.24, 6961.45]</t>
+          <t>[4499.53, 4478.78, 3914.55]</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>[3968.2, 4638.7, 6160.3]</t>
+          <t>[5602.1, 5910.7, 5144.2]</t>
         </is>
       </c>
     </row>
@@ -3070,31 +3070,31 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>912.71</v>
+        <v>1073.4</v>
       </c>
       <c r="E74" t="n">
-        <v>798.91</v>
+        <v>1009.83</v>
       </c>
       <c r="F74" t="n">
-        <v>12.41</v>
+        <v>18.34</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>[4896.28, 6960.81, 8504.44]</t>
+          <t>[4548.1, 3986.23, 4869.86]</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>[4638.7, 6160.3, 7165.8]</t>
+          <t>[5910.7, 5144.2, 5378.8]</t>
         </is>
       </c>
     </row>
@@ -3106,31 +3106,31 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>997.8200000000001</v>
+        <v>664.29</v>
       </c>
       <c r="E75" t="n">
-        <v>972.74</v>
+        <v>545.38</v>
       </c>
       <c r="F75" t="n">
-        <v>13.56</v>
+        <v>10.81</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>[6923.48, 8446.27, 9261.27]</t>
+          <t>[4072.53, 5006.96, 4304.63]</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>[6160.3, 7165.8, 8386.7]</t>
+          <t>[5144.2, 5378.8, 4112.0]</t>
         </is>
       </c>
     </row>
@@ -3142,31 +3142,31 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>870.17</v>
+        <v>417.49</v>
       </c>
       <c r="E76" t="n">
-        <v>813.25</v>
+        <v>389.9</v>
       </c>
       <c r="F76" t="n">
-        <v>10.76</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>[8375.15, 9163.35, 7827.65]</t>
+          <t>[5134.58, 4442.44, 5058.52]</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>[7165.8, 8386.7, 7373.9]</t>
+          <t>[5378.8, 4112.0, 4463.5]</t>
         </is>
       </c>
     </row>
@@ -3178,31 +3178,31 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>500.27</v>
+        <v>696.02</v>
       </c>
       <c r="E77" t="n">
-        <v>475.01</v>
+        <v>654.6799999999999</v>
       </c>
       <c r="F77" t="n">
-        <v>6.55</v>
+        <v>13.92</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>[8963.24, 7627.21, 5776.62]</t>
+          <t>[4486.65, 5100.3, 6135.8]</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>[8386.7, 7373.9, 6371.8]</t>
+          <t>[4112.0, 4463.5, 5183.2]</t>
         </is>
       </c>
     </row>
@@ -3214,31 +3214,31 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>776.22</v>
+        <v>1052.53</v>
       </c>
       <c r="E78" t="n">
-        <v>668.72</v>
+        <v>972.08</v>
       </c>
       <c r="F78" t="n">
-        <v>11.19</v>
+        <v>16.88</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>[7569.89, 5722.44, 4441.29]</t>
+          <t>[5029.71, 6010.68, 8448.74]</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>[7373.9, 6371.8, 5602.1]</t>
+          <t>[4463.5, 5183.2, 6926.2]</t>
         </is>
       </c>
     </row>
@@ -3250,31 +3250,31 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>1171.13</v>
+        <v>1631.97</v>
       </c>
       <c r="E79" t="n">
-        <v>1118.68</v>
+        <v>1495.53</v>
       </c>
       <c r="F79" t="n">
-        <v>19.02</v>
+        <v>21.6</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>[5703.37, 4425.99, 4399.21]</t>
+          <t>[5931.28, 8325.26, 10094.75]</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>[6371.8, 5602.1, 5910.7]</t>
+          <t>[5183.2, 6926.2, 7755.3]</t>
         </is>
       </c>
     </row>
@@ -3286,31 +3286,31 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>1262.02</v>
+        <v>2103.27</v>
       </c>
       <c r="E80" t="n">
-        <v>1254.72</v>
+        <v>2010.97</v>
       </c>
       <c r="F80" t="n">
-        <v>22.6</v>
+        <v>25.99</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>[4499.53, 4478.78, 3914.55]</t>
+          <t>[8141.55, 9856.06, 10868.88]</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>[5602.1, 5910.7, 5144.2]</t>
+          <t>[6926.2, 7755.3, 8152.1]</t>
         </is>
       </c>
     </row>
@@ -3322,31 +3322,31 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>1073.4</v>
+        <v>2131.99</v>
       </c>
       <c r="E81" t="n">
-        <v>1009.83</v>
+        <v>2118.75</v>
       </c>
       <c r="F81" t="n">
-        <v>18.34</v>
+        <v>27.87</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>[4548.1, 3986.23, 4869.86]</t>
+          <t>[9612.83, 10583.91, 8998.1]</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>[5910.7, 5144.2, 5378.8]</t>
+          <t>[7755.3, 8152.1, 6931.2]</t>
         </is>
       </c>
     </row>
@@ -3358,31 +3358,31 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>1757.88</v>
+        <v>2920.15</v>
       </c>
       <c r="E82" t="n">
-        <v>1755.37</v>
+        <v>2823.13</v>
       </c>
       <c r="F82" t="n">
-        <v>14.58</v>
+        <v>12.9</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>[10030.27, 9942.49, 10947.64]</t>
+          <t>[21387.84, 21178.54, 13669.74]</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>[11727.3, 11830.5, 12628.7]</t>
+          <t>[24907.0, 24341.0, 15457.5]</t>
         </is>
       </c>
     </row>
@@ -3394,31 +3394,31 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>2498.07</v>
+        <v>2109.41</v>
       </c>
       <c r="E83" t="n">
-        <v>2339.68</v>
+        <v>2032.25</v>
       </c>
       <c r="F83" t="n">
-        <v>15.41</v>
+        <v>11.18</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>[9969.13, 11038.7, 16348.53]</t>
+          <t>[21515.2, 13906.03, 12732.93]</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>[11830.5, 12628.7, 19916.2]</t>
+          <t>[24341.0, 15457.5, 14452.4]</t>
         </is>
       </c>
     </row>
@@ -3430,31 +3430,31 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>3026.33</v>
+        <v>3027.6</v>
       </c>
       <c r="E84" t="n">
-        <v>2782.08</v>
+        <v>2611.58</v>
       </c>
       <c r="F84" t="n">
-        <v>14.6</v>
+        <v>15.55</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>[11422.59, 16861.18, 17525.8]</t>
+          <t>[14005.21, 12845.82, 13494.94]</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>[12628.7, 19916.2, 21610.9]</t>
+          <t>[15457.5, 14452.4, 18270.8]</t>
         </is>
       </c>
     </row>
@@ -3466,31 +3466,31 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>3926.27</v>
+        <v>3086.86</v>
       </c>
       <c r="E85" t="n">
-        <v>3865.12</v>
+        <v>2766.73</v>
       </c>
       <c r="F85" t="n">
-        <v>16.45</v>
+        <v>17.93</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>[16931.49, 17670.65, 24272.09]</t>
+          <t>[12909.7, 13593.12, 9790.7]</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>[19916.2, 21610.9, 28942.5]</t>
+          <t>[14452.4, 18270.8, 11870.5]</t>
         </is>
       </c>
     </row>
@@ -3502,31 +3502,31 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>4102.83</v>
+        <v>3178.84</v>
       </c>
       <c r="E86" t="n">
-        <v>4096.52</v>
+        <v>2961.3</v>
       </c>
       <c r="F86" t="n">
-        <v>17.07</v>
+        <v>20.39</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>[17767.83, 24547.53, 18156.8]</t>
+          <t>[13687.91, 9897.25, 9622.55]</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>[21610.9, 28942.5, 22208.3]</t>
+          <t>[18270.8, 11870.5, 11950.3]</t>
         </is>
       </c>
     </row>
@@ -3538,31 +3538,31 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>3934.1</v>
+        <v>1769.28</v>
       </c>
       <c r="E87" t="n">
-        <v>3927.37</v>
+        <v>1763.01</v>
       </c>
       <c r="F87" t="n">
-        <v>15.63</v>
+        <v>14.43</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>[25030.77, 18554.39, 20690.52]</t>
+          <t>[10317.49, 10095.38, 10923.71]</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>[28942.5, 22208.3, 24907.0]</t>
+          <t>[11870.5, 11950.3, 12804.8]</t>
         </is>
       </c>
     </row>
@@ -3574,31 +3574,31 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>3604.37</v>
+        <v>2267.38</v>
       </c>
       <c r="E88" t="n">
-        <v>3598.26</v>
+        <v>2140.84</v>
       </c>
       <c r="F88" t="n">
-        <v>15.11</v>
+        <v>13.94</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>[18827.78, 21025.19, 20808.56]</t>
+          <t>[10329.68, 11199.94, 17128.27]</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>[22208.3, 24907.0, 24341.0]</t>
+          <t>[11950.3, 12804.8, 20325.3]</t>
         </is>
       </c>
     </row>
@@ -3610,31 +3610,31 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>2920.15</v>
+        <v>2102.55</v>
       </c>
       <c r="E89" t="n">
-        <v>2823.13</v>
+        <v>2019.11</v>
       </c>
       <c r="F89" t="n">
-        <v>12.9</v>
+        <v>10.8</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>[21387.84, 21178.54, 13669.74]</t>
+          <t>[11606.4, 17792.61, 19640.34]</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>[24907.0, 24341.0, 15457.5]</t>
+          <t>[12804.8, 20325.3, 21966.6]</t>
         </is>
       </c>
     </row>
@@ -3646,31 +3646,31 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>2109.41</v>
+        <v>1772.51</v>
       </c>
       <c r="E90" t="n">
-        <v>2032.25</v>
+        <v>1717.54</v>
       </c>
       <c r="F90" t="n">
-        <v>11.18</v>
+        <v>7.13</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>[21515.2, 13906.03, 12732.93]</t>
+          <t>[18724.53, 20717.5, 27125.35]</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>[24341.0, 15457.5, 14452.4]</t>
+          <t>[20325.3, 21966.6, 29428.1]</t>
         </is>
       </c>
     </row>
@@ -3682,31 +3682,31 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>3027.6</v>
+        <v>1147.25</v>
       </c>
       <c r="E91" t="n">
-        <v>2611.58</v>
+        <v>1097.5</v>
       </c>
       <c r="F91" t="n">
-        <v>15.55</v>
+        <v>4.37</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>[14005.21, 12845.82, 13494.94]</t>
+          <t>[21290.84, 27934.98, 21514.8]</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>[15457.5, 14452.4, 18270.8]</t>
+          <t>[21966.6, 29428.1, 22638.4]</t>
         </is>
       </c>
     </row>
@@ -3718,31 +3718,31 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>782.22</v>
+        <v>2083.37</v>
       </c>
       <c r="E92" t="n">
-        <v>610.7</v>
+        <v>2071.89</v>
       </c>
       <c r="F92" t="n">
-        <v>10.09</v>
+        <v>12.72</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>[3422.82, 5144.44, 8407.58]</t>
+          <t>[22414.55, 21816.96, 12937.47]</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>[3219.2, 6442.5, 8738.0]</t>
+          <t>[20199.8, 19579.4, 11174.1]</t>
         </is>
       </c>
     </row>
@@ -3754,31 +3754,31 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>1398.26</v>
+        <v>1487.48</v>
       </c>
       <c r="E93" t="n">
-        <v>1248.62</v>
+        <v>1243.19</v>
       </c>
       <c r="F93" t="n">
-        <v>12.12</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>[5087.19, 8307.95, 16871.89]</t>
+          <t>[21584.36, 12788.33, 9526.27]</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>[6442.5, 8738.0, 18832.4]</t>
+          <t>[19579.4, 11174.1, 9415.9]</t>
         </is>
       </c>
     </row>
@@ -3790,31 +3790,31 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>1573.75</v>
+        <v>996.67</v>
       </c>
       <c r="E94" t="n">
-        <v>1274.58</v>
+        <v>795.16</v>
       </c>
       <c r="F94" t="n">
-        <v>5.1</v>
+        <v>7.52</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>[8620.45, 17502.89, 32082.42]</t>
+          <t>[12667.56, 9442.51, 8847.0]</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>[8738.0, 18832.4, 34459.1]</t>
+          <t>[11174.1, 9415.9, 9712.4]</t>
         </is>
       </c>
     </row>
@@ -3826,31 +3826,31 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>1591.88</v>
+        <v>560.74</v>
       </c>
       <c r="E95" t="n">
-        <v>1404.63</v>
+        <v>350.99</v>
       </c>
       <c r="F95" t="n">
-        <v>5.07</v>
+        <v>3.75</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>[17518.62, 32095.01, 38770.97]</t>
+          <t>[9351.05, 8743.53, 3230.44]</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>[18832.4, 34459.1, 39307.0]</t>
+          <t>[9415.9, 9712.4, 3211.2]</t>
         </is>
       </c>
     </row>
@@ -3862,31 +3862,31 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>1296.52</v>
+        <v>766.45</v>
       </c>
       <c r="E96" t="n">
-        <v>988.03</v>
+        <v>631.34</v>
       </c>
       <c r="F96" t="n">
-        <v>2.96</v>
+        <v>8.08</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>[32288.6, 39002.13, 27517.3]</t>
+          <t>[8739.93, 3229.26, 5705.61]</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>[34459.1, 39307.0, 27028.6]</t>
+          <t>[9712.4, 3211.2, 6609.1]</t>
         </is>
       </c>
     </row>
@@ -3898,31 +3898,31 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>1319</v>
+        <v>765.77</v>
       </c>
       <c r="E97" t="n">
-        <v>995.6</v>
+        <v>638.74</v>
       </c>
       <c r="F97" t="n">
-        <v>4.52</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>[39108.23, 27618.48, 22397.94]</t>
+          <t>[3264.45, 5780.25, 8033.19]</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>[39307.0, 27028.6, 20199.8]</t>
+          <t>[3211.2, 6609.1, 9067.3]</t>
         </is>
       </c>
     </row>
@@ -3934,31 +3934,31 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>1895.92</v>
+        <v>1739.52</v>
       </c>
       <c r="E98" t="n">
-        <v>1736.47</v>
+        <v>1523.75</v>
       </c>
       <c r="F98" t="n">
-        <v>8.44</v>
+        <v>12.66</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>[27688.94, 22460.33, 21867.95]</t>
+          <t>[5780.41, 8028.98, 16638.26]</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>[27028.6, 20199.8, 19579.4]</t>
+          <t>[6609.1, 9067.3, 19342.5]</t>
         </is>
       </c>
     </row>
@@ -3970,31 +3970,31 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>2083.37</v>
+        <v>2785.95</v>
       </c>
       <c r="E99" t="n">
-        <v>2071.89</v>
+        <v>2489.6</v>
       </c>
       <c r="F99" t="n">
-        <v>12.72</v>
+        <v>11.59</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>[22414.55, 21816.96, 12937.47]</t>
+          <t>[8114.69, 16841.6, 31406.51]</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>[20199.8, 19579.4, 11174.1]</t>
+          <t>[9067.3, 19342.5, 35421.8]</t>
         </is>
       </c>
     </row>
@@ -4006,31 +4006,31 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>1487.48</v>
+        <v>3519.91</v>
       </c>
       <c r="E100" t="n">
-        <v>1243.19</v>
+        <v>3417.96</v>
       </c>
       <c r="F100" t="n">
-        <v>8.619999999999999</v>
+        <v>10.96</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>[21584.36, 12788.33, 9526.27]</t>
+          <t>[17042.22, 31797.34, 35916.77]</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>[19579.4, 11174.1, 9415.9]</t>
+          <t>[19342.5, 35421.8, 40245.9]</t>
         </is>
       </c>
     </row>
@@ -4042,31 +4042,31 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>996.67</v>
+        <v>3107.27</v>
       </c>
       <c r="E101" t="n">
-        <v>795.16</v>
+        <v>2964.57</v>
       </c>
       <c r="F101" t="n">
-        <v>7.52</v>
+        <v>8.34</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>[12667.56, 9442.51, 8847.0]</t>
+          <t>[32147.21, 36328.37, 26432.92]</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>[11174.1, 9415.9, 9712.4]</t>
+          <t>[35421.8, 40245.9, 28134.5]</t>
         </is>
       </c>
     </row>
@@ -4078,31 +4078,31 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>3121.51</v>
+        <v>6859.22</v>
       </c>
       <c r="E102" t="n">
-        <v>2739.08</v>
+        <v>6304.4</v>
       </c>
       <c r="F102" t="n">
-        <v>29.2</v>
+        <v>33.25</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>[3340.59, 4685.5, 11546.47]</t>
+          <t>[14044.05, 13265.29, 9126.58]</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>[4432.0, 7097.0, 16260.8]</t>
+          <t>[18272.4, 23386.7, 13690.0]</t>
         </is>
       </c>
     </row>
@@ -4114,31 +4114,31 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>4189.21</v>
+        <v>6610.09</v>
       </c>
       <c r="E103" t="n">
-        <v>4005.51</v>
+        <v>6063.04</v>
       </c>
       <c r="F103" t="n">
-        <v>30.89</v>
+        <v>35.71</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>[4737.13, 11908.93, 10939.02]</t>
+          <t>[13602.09, 9379.99, 8020.49]</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>[7097.0, 16260.8, 16243.8]</t>
+          <t>[23386.7, 13690.0, 12115.0]</t>
         </is>
       </c>
     </row>
@@ -4150,31 +4150,31 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>5663.14</v>
+        <v>5662.27</v>
       </c>
       <c r="E104" t="n">
-        <v>5352.48</v>
+        <v>5313.82</v>
       </c>
       <c r="F104" t="n">
-        <v>27.53</v>
+        <v>33.23</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>[12716.06, 11625.21, 16510.09]</t>
+          <t>[9643.37, 8296.58, 12842.29]</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>[16260.8, 16243.8, 24404.2]</t>
+          <t>[13690.0, 12115.0, 20918.7]</t>
         </is>
       </c>
     </row>
@@ -4186,31 +4186,31 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>7665.9</v>
+        <v>4981.3</v>
       </c>
       <c r="E105" t="n">
-        <v>7286.69</v>
+        <v>4247.26</v>
       </c>
       <c r="F105" t="n">
-        <v>29.55</v>
+        <v>32.95</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>[11891.64, 17080.81, 21801.78]</t>
+          <t>[8494.31, 13217.01, 2994.09]</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>[16243.8, 24404.2, 31986.3]</t>
+          <t>[12115.0, 20918.7, 4413.5]</t>
         </is>
       </c>
     </row>
@@ -4222,31 +4222,31 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>7852.23</v>
+        <v>4213.48</v>
       </c>
       <c r="E106" t="n">
-        <v>7780.62</v>
+        <v>3274.95</v>
       </c>
       <c r="F106" t="n">
-        <v>29.86</v>
+        <v>27.94</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>[17591.15, 22733.49, 14959.39]</t>
+          <t>[13899.68, 3179.9, 5472.98]</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>[24404.2, 31986.3, 22235.4]</t>
+          <t>[20918.7, 4413.5, 7045.2]</t>
         </is>
       </c>
     </row>
@@ -4258,31 +4258,31 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>6683.72</v>
+        <v>2183.48</v>
       </c>
       <c r="E107" t="n">
-        <v>6541.02</v>
+        <v>1841.5</v>
       </c>
       <c r="F107" t="n">
-        <v>27.24</v>
+        <v>19.39</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>[23770.29, 15679.46, 13421.29]</t>
+          <t>[3450.09, 5983.85, 12938.77]</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>[31986.3, 22235.4, 18272.4]</t>
+          <t>[4413.5, 7045.2, 16438.5]</t>
         </is>
       </c>
     </row>
@@ -4294,31 +4294,31 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>7446.19</v>
+        <v>2589.41</v>
       </c>
       <c r="E108" t="n">
-        <v>7024.84</v>
+        <v>2324.08</v>
       </c>
       <c r="F108" t="n">
-        <v>32.3</v>
+        <v>16.1</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>[16061.17, 13755.42, 13003.39]</t>
+          <t>[6294.57, 13641.94, 13168.26]</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>[22235.4, 18272.4, 23386.7]</t>
+          <t>[7045.2, 16438.5, 16593.3]</t>
         </is>
       </c>
     </row>
@@ -4330,31 +4330,31 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>6859.22</v>
+        <v>2472.71</v>
       </c>
       <c r="E109" t="n">
-        <v>6304.4</v>
+        <v>2412.39</v>
       </c>
       <c r="F109" t="n">
-        <v>33.25</v>
+        <v>12.48</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>[14044.05, 13265.29, 9126.58]</t>
+          <t>[14677.3, 14207.44, 21918.29]</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>[18272.4, 23386.7, 13690.0]</t>
+          <t>[16438.5, 16593.3, 25008.4]</t>
         </is>
       </c>
     </row>
@@ -4366,31 +4366,31 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>6610.09</v>
+        <v>2562.08</v>
       </c>
       <c r="E110" t="n">
-        <v>6063.04</v>
+        <v>2264.05</v>
       </c>
       <c r="F110" t="n">
-        <v>35.71</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>[13602.09, 9379.99, 8020.49]</t>
+          <t>[15206.09, 23563.27, 29091.5]</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>[23386.7, 13690.0, 12115.0]</t>
+          <t>[16593.3, 25008.4, 33051.3]</t>
         </is>
       </c>
     </row>
@@ -4402,31 +4402,31 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>5662.27</v>
+        <v>1530.79</v>
       </c>
       <c r="E111" t="n">
-        <v>5313.82</v>
+        <v>1244.25</v>
       </c>
       <c r="F111" t="n">
-        <v>33.23</v>
+        <v>4.35</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>[9643.37, 8296.58, 12842.29]</t>
+          <t>[24695.42, 30605.01, 21140.83]</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>[13690.0, 12115.0, 20918.7]</t>
+          <t>[25008.4, 33051.3, 22114.3]</t>
         </is>
       </c>
     </row>
@@ -4438,31 +4438,31 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>3304.28</v>
+        <v>3796.84</v>
       </c>
       <c r="E112" t="n">
-        <v>3288.41</v>
+        <v>3795.99</v>
       </c>
       <c r="F112" t="n">
-        <v>25.83</v>
+        <v>30.41</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>[8234.42, 9737.54, 10347.52]</t>
+          <t>[9512.59, 9076.69, 7625.64]</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>[11065.4, 13251.6, 13867.7]</t>
+          <t>[13406.8, 12774.7, 11421.4]</t>
         </is>
       </c>
     </row>
@@ -4474,31 +4474,31 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>3051.08</v>
+        <v>3438.21</v>
       </c>
       <c r="E113" t="n">
-        <v>3049.77</v>
+        <v>3437.84</v>
       </c>
       <c r="F113" t="n">
-        <v>19.55</v>
+        <v>32.96</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>[10075.5, 10876.2, 19777.8]</t>
+          <t>[9405.54, 7933.83, 4779.61]</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>[13251.6, 13867.7, 22759.5]</t>
+          <t>[12774.7, 11421.4, 8236.4]</t>
         </is>
       </c>
     </row>
@@ -4510,31 +4510,31 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>3216.06</v>
+        <v>3064.69</v>
       </c>
       <c r="E114" t="n">
-        <v>3088.57</v>
+        <v>3039.41</v>
       </c>
       <c r="F114" t="n">
-        <v>16.16</v>
+        <v>31.54</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>[11288.94, 20421.4, 17827.66]</t>
+          <t>[8117.33, 4906.29, 7355.76]</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>[13867.7, 22759.5, 22176.5]</t>
+          <t>[11421.4, 8236.4, 9839.8]</t>
         </is>
       </c>
     </row>
@@ -4546,31 +4546,31 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>2595.86</v>
+        <v>3664.59</v>
       </c>
       <c r="E115" t="n">
-        <v>2042.71</v>
+        <v>3501.36</v>
       </c>
       <c r="F115" t="n">
-        <v>9</v>
+        <v>34.39</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>[20913.43, 18081.05, 43393.0]</t>
+          <t>[4988.49, 7518.02, 7362.31]</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>[22759.5, 22176.5, 43579.6]</t>
+          <t>[8236.4, 9839.8, 12296.7]</t>
         </is>
       </c>
     </row>
@@ -4582,31 +4582,31 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>3472.28</v>
+        <v>3844.22</v>
       </c>
       <c r="E116" t="n">
-        <v>2886.34</v>
+        <v>3672.33</v>
       </c>
       <c r="F116" t="n">
-        <v>12.48</v>
+        <v>29.43</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>[17957.29, 43422.79, 19440.62]</t>
+          <t>[7762.97, 7656.95, 10308.07]</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>[22176.5, 43579.6, 23723.6]</t>
+          <t>[9839.8, 12296.7, 14608.5]</t>
         </is>
       </c>
     </row>
@@ -4618,31 +4618,31 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>3208.02</v>
+        <v>4670.97</v>
       </c>
       <c r="E117" t="n">
-        <v>2833.94</v>
+        <v>4648.89</v>
       </c>
       <c r="F117" t="n">
-        <v>15.8</v>
+        <v>33.02</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>[44289.94, 19917.1, 9421.82]</t>
+          <t>[7777.4, 10438.95, 10313.28]</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>[43579.6, 23723.6, 13406.8]</t>
+          <t>[12296.7, 14608.5, 15571.1]</t>
         </is>
       </c>
     </row>
@@ -4654,31 +4654,31 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>4008.91</v>
+        <v>4861.13</v>
       </c>
       <c r="E118" t="n">
-        <v>4007.62</v>
+        <v>4776.03</v>
       </c>
       <c r="F118" t="n">
-        <v>26.01</v>
+        <v>26.2</v>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>[19692.65, 9288.16, 8901.43]</t>
+          <t>[10890.79, 10890.46, 19735.46]</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>[23723.6, 13406.8, 12774.7]</t>
+          <t>[14608.5, 15571.1, 25665.2]</t>
         </is>
       </c>
     </row>
@@ -4690,31 +4690,31 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>3796.84</v>
+        <v>4274</v>
       </c>
       <c r="E119" t="n">
-        <v>3795.99</v>
+        <v>4263.85</v>
       </c>
       <c r="F119" t="n">
-        <v>30.41</v>
+        <v>20.19</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>[9512.59, 9076.69, 7625.64]</t>
+          <t>[11520.91, 20985.04, 20801.6]</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>[13406.8, 12774.7, 11421.4]</t>
+          <t>[15571.1, 25665.2, 24862.8]</t>
         </is>
       </c>
     </row>
@@ -4726,31 +4726,31 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>3438.21</v>
+        <v>2978.28</v>
       </c>
       <c r="E120" t="n">
-        <v>3437.84</v>
+        <v>2923.65</v>
       </c>
       <c r="F120" t="n">
-        <v>32.96</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>[9405.54, 7933.83, 4779.61]</t>
+          <t>[22755.24, 22627.59, 44729.6]</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>[12774.7, 11421.4, 8236.4]</t>
+          <t>[25665.2, 24862.8, 48355.4]</t>
         </is>
       </c>
     </row>
@@ -4762,31 +4762,31 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>3064.69</v>
+        <v>433.82</v>
       </c>
       <c r="E121" t="n">
-        <v>3039.41</v>
+        <v>399.33</v>
       </c>
       <c r="F121" t="n">
-        <v>31.54</v>
+        <v>1.45</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>[8117.33, 4906.29, 7355.76]</t>
+          <t>[24569.55, 48621.58, 25072.95]</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>[11421.4, 8236.4, 9839.8]</t>
+          <t>[24862.8, 48355.4, 24434.4]</t>
         </is>
       </c>
     </row>
@@ -4798,31 +4798,31 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>264.77</v>
+        <v>572.14</v>
       </c>
       <c r="E122" t="n">
-        <v>244.12</v>
+        <v>570.6900000000001</v>
       </c>
       <c r="F122" t="n">
-        <v>8.18</v>
+        <v>13.26</v>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>[2634.5, 2630.68, 3111.65]</t>
+          <t>[3849.0, 3771.05, 3590.88]</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>[2911.0, 2981.0, 3217.2]</t>
+          <t>[4363.4, 4359.7, 4199.9]</t>
         </is>
       </c>
     </row>
@@ -4834,31 +4834,31 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>238.29</v>
+        <v>567.58</v>
       </c>
       <c r="E123" t="n">
-        <v>208.82</v>
+        <v>567.09</v>
       </c>
       <c r="F123" t="n">
-        <v>6.5</v>
+        <v>13.12</v>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>[2651.23, 3162.6, 3350.49]</t>
+          <t>[3819.57, 3636.0, 3811.24]</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>[2981.0, 3217.2, 3592.6]</t>
+          <t>[4359.7, 4199.9, 4408.5]</t>
         </is>
       </c>
     </row>
@@ -4870,31 +4870,31 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>283.26</v>
+        <v>1245.93</v>
       </c>
       <c r="E124" t="n">
-        <v>233.55</v>
+        <v>1044.18</v>
       </c>
       <c r="F124" t="n">
-        <v>6.28</v>
+        <v>20.57</v>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>[3178.4, 3362.15, 3418.2]</t>
+          <t>[3646.76, 3834.47, 3641.23]</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>[3217.2, 3592.6, 3849.6]</t>
+          <t>[4199.9, 4408.5, 5646.6]</t>
         </is>
       </c>
     </row>
@@ -4906,31 +4906,31 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>422.63</v>
+        <v>1253.87</v>
       </c>
       <c r="E125" t="n">
-        <v>398.28</v>
+        <v>1053.13</v>
       </c>
       <c r="F125" t="n">
-        <v>9.970000000000001</v>
+        <v>22.74</v>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>[3376.72, 3430.99, 3740.84]</t>
+          <t>[3880.25, 3632.44, 2383.23]</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>[3592.6, 3849.6, 4301.2]</t>
+          <t>[4408.5, 5646.6, 3000.2]</t>
         </is>
       </c>
     </row>
@@ -4942,31 +4942,31 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>543.74</v>
+        <v>1237.37</v>
       </c>
       <c r="E126" t="n">
-        <v>536.77</v>
+        <v>1080.81</v>
       </c>
       <c r="F126" t="n">
-        <v>12.85</v>
+        <v>25.88</v>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>[3429.89, 3737.92, 3682.58]</t>
+          <t>[3717.45, 2411.66, 2311.47]</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>[3849.6, 4301.2, 4309.9]</t>
+          <t>[5646.6, 3000.2, 3036.2]</t>
         </is>
       </c>
     </row>
@@ -4978,31 +4978,31 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>569.9</v>
+        <v>568.98</v>
       </c>
       <c r="E127" t="n">
-        <v>569.1</v>
+        <v>566.61</v>
       </c>
       <c r="F127" t="n">
-        <v>13.16</v>
+        <v>18.43</v>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>[3774.05, 3727.26, 3765.9]</t>
+          <t>[2487.1, 2399.37, 2645.8]</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>[4301.2, 4309.9, 4363.4]</t>
+          <t>[3000.2, 3036.2, 3195.7]</t>
         </is>
       </c>
     </row>
@@ -5014,31 +5014,31 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>593.95</v>
+        <v>604.05</v>
       </c>
       <c r="E128" t="n">
-        <v>592.95</v>
+        <v>600.36</v>
       </c>
       <c r="F128" t="n">
-        <v>13.65</v>
+        <v>18.33</v>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>[3745.1, 3790.94, 3718.11]</t>
+          <t>[2423.36, 2682.55, 2926.02]</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>[4309.9, 4363.4, 4359.7]</t>
+          <t>[3036.2, 3195.7, 3601.1]</t>
         </is>
       </c>
     </row>
@@ -5050,31 +5050,31 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>572.14</v>
+        <v>559.4400000000001</v>
       </c>
       <c r="E129" t="n">
-        <v>570.6900000000001</v>
+        <v>550.2</v>
       </c>
       <c r="F129" t="n">
-        <v>13.26</v>
+        <v>15.32</v>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>[3849.0, 3771.05, 3590.88]</t>
+          <t>[2774.9, 3039.22, 3219.47]</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>[4363.4, 4359.7, 4199.9]</t>
+          <t>[3195.7, 3601.1, 3887.4]</t>
         </is>
       </c>
     </row>
@@ -5086,31 +5086,31 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>567.58</v>
+        <v>758.02</v>
       </c>
       <c r="E130" t="n">
-        <v>567.09</v>
+        <v>702.8099999999999</v>
       </c>
       <c r="F130" t="n">
-        <v>13.12</v>
+        <v>16.67</v>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>[3819.57, 3636.0, 3811.24]</t>
+          <t>[3143.94, 3336.94, 3653.48]</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>[4359.7, 4199.9, 4408.5]</t>
+          <t>[3601.1, 3887.4, 4754.3]</t>
         </is>
       </c>
     </row>
@@ -5122,31 +5122,31 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>1245.93</v>
+        <v>699.54</v>
       </c>
       <c r="E131" t="n">
-        <v>1044.18</v>
+        <v>660.2</v>
       </c>
       <c r="F131" t="n">
-        <v>20.57</v>
+        <v>14.49</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>[3646.76, 3834.47, 3641.23]</t>
+          <t>[3553.11, 3907.31, 3883.58]</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>[4199.9, 4408.5, 5646.6]</t>
+          <t>[3887.4, 4754.3, 4682.9]</t>
         </is>
       </c>
     </row>
@@ -5158,12 +5158,12 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5179,7 +5179,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[0.0, 0.0, -0.0]</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -5196,12 +5196,12 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5217,7 +5217,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[0.0, -0.0, -0.0]</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -5234,12 +5234,12 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5255,7 +5255,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[-0.0, -0.0, -0.0]</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -5272,12 +5272,12 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5293,7 +5293,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[-0.0, -0.0, -0.0]</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -5310,12 +5310,12 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5331,7 +5331,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[-0.0, -0.0, -0.0]</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5369,7 +5369,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[-0.0, -0.0, -0.0]</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -5386,12 +5386,12 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5407,7 +5407,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[-0.0, -0.0, -0.0]</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -5424,12 +5424,12 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5445,7 +5445,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, -0.0]</t>
+          <t>[-0.0, -0.0, 0.0]</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5483,7 +5483,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>[0.0, -0.0, -0.0]</t>
+          <t>[-0.0, 0.0, -0.0]</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -5500,12 +5500,12 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5521,7 +5521,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>[-0.0, -0.0, -0.0]</t>
+          <t>[0.0, -0.0, -0.0]</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -5538,31 +5538,31 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D142" t="n">
-        <v>5735.5</v>
+        <v>9599.43</v>
       </c>
       <c r="E142" t="n">
-        <v>5482.35</v>
+        <v>9411.870000000001</v>
       </c>
       <c r="F142" t="n">
-        <v>44.94</v>
+        <v>32.84</v>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>[16787.14, 15798.46, 14926.35]</t>
+          <t>[25541.01, 19716.48, 14567.21]</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>[9299.7, 12434.2, 20521.7]</t>
+          <t>[32329.0, 30870.5, 24860.8]</t>
         </is>
       </c>
     </row>
@@ -5574,31 +5574,31 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D143" t="n">
-        <v>8786.290000000001</v>
+        <v>9003.02</v>
       </c>
       <c r="E143" t="n">
-        <v>7399.91</v>
+        <v>8978.879999999999</v>
       </c>
       <c r="F143" t="n">
-        <v>33.57</v>
+        <v>36.36</v>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>[14059.53, 13175.74, 12292.35]</t>
+          <t>[20966.15, 16438.98, 28572.27]</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>[12434.2, 20521.7, 25520.8]</t>
+          <t>[30870.5, 24860.8, 19961.8]</t>
         </is>
       </c>
     </row>
@@ -5610,31 +5610,31 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D144" t="n">
-        <v>13803.15</v>
+        <v>29139</v>
       </c>
       <c r="E144" t="n">
-        <v>13115.82</v>
+        <v>23599.27</v>
       </c>
       <c r="F144" t="n">
-        <v>50.73</v>
+        <v>131.55</v>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>[12870.35, 11987.49, 11190.81]</t>
+          <t>[29329.03, 40330.65, 62696.33]</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>[20521.7, 25520.8, 29353.6]</t>
+          <t>[24860.8, 19961.8, 16735.6]</t>
         </is>
       </c>
     </row>
@@ -5646,31 +5646,31 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D145" t="n">
-        <v>20406.9</v>
+        <v>27190.83</v>
       </c>
       <c r="E145" t="n">
-        <v>19298.6</v>
+        <v>21536.32</v>
       </c>
       <c r="F145" t="n">
-        <v>59.47</v>
+        <v>129.79</v>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>[13034.62, 12234.64, 11459.54]</t>
+          <t>[36415.77, 60660.49, 5279.71]</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>[25520.8, 29353.6, 39750.2]</t>
+          <t>[19961.8, 16735.6, 9509.8]</t>
         </is>
       </c>
     </row>
@@ -5682,31 +5682,31 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D146" t="n">
-        <v>21933.22</v>
+        <v>10463.03</v>
       </c>
       <c r="E146" t="n">
-        <v>21450.69</v>
+        <v>9554.83</v>
       </c>
       <c r="F146" t="n">
-        <v>61.56</v>
+        <v>71.18000000000001</v>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>[13748.75, 12974.43, 12266.64]</t>
+          <t>[32320.18, 3012.12, 6055.96]</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>[29353.6, 39750.2, 34238.1]</t>
+          <t>[16735.6, 9509.8, 12638.2]</t>
         </is>
       </c>
     </row>
@@ -5718,31 +5718,31 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D147" t="n">
-        <v>20506.71</v>
+        <v>6707.91</v>
       </c>
       <c r="E147" t="n">
-        <v>20332.2</v>
+        <v>6603.85</v>
       </c>
       <c r="F147" t="n">
-        <v>57.17</v>
+        <v>49.1</v>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>[15718.05, 15105.35, 14497.3]</t>
+          <t>[3275.94, 7254.75, 12738.17]</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>[39750.2, 34238.1, 32329.0]</t>
+          <t>[9509.8, 12638.2, 20932.4]</t>
         </is>
       </c>
     </row>
@@ -5754,31 +5754,31 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D148" t="n">
-        <v>12017.98</v>
+        <v>4547.11</v>
       </c>
       <c r="E148" t="n">
-        <v>11196.29</v>
+        <v>4356.8</v>
       </c>
       <c r="F148" t="n">
-        <v>35.1</v>
+        <v>26.05</v>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>[28248.99, 21405.94, 14193.79]</t>
+          <t>[6483.37, 17816.87, 22304.47]</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>[34238.1, 32329.0, 30870.5]</t>
+          <t>[12638.2, 20932.4, 26104.5]</t>
         </is>
       </c>
     </row>
@@ -5790,31 +5790,31 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D149" t="n">
-        <v>9599.43</v>
+        <v>478.3</v>
       </c>
       <c r="E149" t="n">
-        <v>9411.870000000001</v>
+        <v>420.85</v>
       </c>
       <c r="F149" t="n">
-        <v>32.84</v>
+        <v>1.81</v>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>[25541.01, 19716.48, 14567.21]</t>
+          <t>[20201.47, 25765.39, 29833.78]</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>[32329.0, 30870.5, 24860.8]</t>
+          <t>[20932.4, 26104.5, 30026.3]</t>
         </is>
       </c>
     </row>
@@ -5826,31 +5826,31 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D150" t="n">
-        <v>9003.02</v>
+        <v>2461.35</v>
       </c>
       <c r="E150" t="n">
-        <v>8978.879999999999</v>
+        <v>1511.42</v>
       </c>
       <c r="F150" t="n">
-        <v>36.36</v>
+        <v>3.61</v>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>[20966.15, 16438.98, 28572.27]</t>
+          <t>[25888.06, 29965.72, 39131.55]</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>[30870.5, 24860.8, 19961.8]</t>
+          <t>[26104.5, 30026.3, 43388.8]</t>
         </is>
       </c>
     </row>
@@ -5862,31 +5862,31 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D151" t="n">
-        <v>29139</v>
+        <v>2997.03</v>
       </c>
       <c r="E151" t="n">
-        <v>23599.27</v>
+        <v>2456.97</v>
       </c>
       <c r="F151" t="n">
-        <v>131.55</v>
+        <v>6.09</v>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>[29329.03, 40330.65, 62696.33]</t>
+          <t>[29634.06, 38794.54, 35050.98]</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>[24860.8, 19961.8, 16735.6]</t>
+          <t>[30026.3, 43388.8, 37435.4]</t>
         </is>
       </c>
     </row>
@@ -5898,31 +5898,31 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D152" t="n">
-        <v>6133.19</v>
+        <v>3440.01</v>
       </c>
       <c r="E152" t="n">
-        <v>5284.73</v>
+        <v>2597.55</v>
       </c>
       <c r="F152" t="n">
-        <v>52.3</v>
+        <v>11.21</v>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>[17430.08, 17390.52, 17353.59]</t>
+          <t>[20442.08, 19577.49, 16882.58]</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>[10557.7, 9344.2, 16418.1]</t>
+          <t>[20792.5, 25258.8, 18643.5]</t>
         </is>
       </c>
     </row>
@@ -5934,31 +5934,31 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D153" t="n">
-        <v>4738.39</v>
+        <v>3071.45</v>
       </c>
       <c r="E153" t="n">
-        <v>4473.82</v>
+        <v>2915.27</v>
       </c>
       <c r="F153" t="n">
-        <v>32.98</v>
+        <v>14.61</v>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>[14416.28, 14083.92, 13737.1]</t>
+          <t>[21843.63, 14875.88, 17057.91]</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>[9344.2, 16418.1, 19752.3]</t>
+          <t>[25258.8, 18643.5, 15494.9]</t>
         </is>
       </c>
     </row>
@@ -5970,31 +5970,31 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D154" t="n">
-        <v>6906.12</v>
+        <v>4035.64</v>
       </c>
       <c r="E154" t="n">
-        <v>6703.89</v>
+        <v>3065.97</v>
       </c>
       <c r="F154" t="n">
-        <v>36.28</v>
+        <v>20.16</v>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>[12019.9, 11519.62, 11055.31]</t>
+          <t>[17301.75, 16577.0, 21405.76]</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>[16418.1, 19752.3, 18536.1]</t>
+          <t>[18643.5, 15494.9, 14631.7]</t>
         </is>
       </c>
     </row>
@@ -6006,31 +6006,31 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D155" t="n">
-        <v>9903.57</v>
+        <v>9664.690000000001</v>
       </c>
       <c r="E155" t="n">
-        <v>9272.280000000001</v>
+        <v>8161.52</v>
       </c>
       <c r="F155" t="n">
-        <v>42</v>
+        <v>56.52</v>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>[12527.77, 12114.64, 11702.04]</t>
+          <t>[22957.23, 29453.68, 8746.97]</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>[19752.3, 18536.1, 25872.9]</t>
+          <t>[15494.9, 14631.7, 10947.2]</t>
         </is>
       </c>
     </row>
@@ -6042,31 +6042,31 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D156" t="n">
-        <v>9204.700000000001</v>
+        <v>4919.87</v>
       </c>
       <c r="E156" t="n">
-        <v>8651.27</v>
+        <v>4403.88</v>
       </c>
       <c r="F156" t="n">
-        <v>38.39</v>
+        <v>35.49</v>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>[13516.51, 13185.12, 12872.16]</t>
+          <t>[22136.98, 8142.62, 12719.8]</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>[18536.1, 25872.9, 21118.6]</t>
+          <t>[14631.7, 10947.2, 9818.0]</t>
         </is>
       </c>
     </row>
@@ -6078,31 +6078,31 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D157" t="n">
-        <v>8907.059999999999</v>
+        <v>4522.57</v>
       </c>
       <c r="E157" t="n">
-        <v>8646.41</v>
+        <v>4156.51</v>
       </c>
       <c r="F157" t="n">
-        <v>37.73</v>
+        <v>33.02</v>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>[14201.75, 13949.49, 13693.53]</t>
+          <t>[5325.24, 8170.42, 11612.41]</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>[25872.9, 21118.6, 20792.5]</t>
+          <t>[10947.2, 9818.0, 16812.4]</t>
         </is>
       </c>
     </row>
@@ -6114,31 +6114,31 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D158" t="n">
-        <v>4965.06</v>
+        <v>350.36</v>
       </c>
       <c r="E158" t="n">
-        <v>4308.05</v>
+        <v>273.68</v>
       </c>
       <c r="F158" t="n">
-        <v>18.51</v>
+        <v>1.56</v>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>[19378.99, 17247.45, 17619.32]</t>
+          <t>[9742.51, 16979.47, 20404.59]</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>[21118.6, 20792.5, 25258.8]</t>
+          <t>[9818.0, 16812.4, 19826.1]</t>
         </is>
       </c>
     </row>
@@ -6150,31 +6150,31 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D159" t="n">
-        <v>3440.01</v>
+        <v>366.1</v>
       </c>
       <c r="E159" t="n">
-        <v>2597.55</v>
+        <v>278.53</v>
       </c>
       <c r="F159" t="n">
-        <v>11.21</v>
+        <v>1.46</v>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>[20442.08, 19577.49, 16882.58]</t>
+          <t>[16998.96, 20430.49, 19191.83]</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>[20792.5, 25258.8, 18643.5]</t>
+          <t>[16812.4, 19826.1, 19147.2]</t>
         </is>
       </c>
     </row>
@@ -6186,31 +6186,31 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D160" t="n">
-        <v>3071.45</v>
+        <v>307.22</v>
       </c>
       <c r="E160" t="n">
-        <v>2915.27</v>
+        <v>259.81</v>
       </c>
       <c r="F160" t="n">
-        <v>14.61</v>
+        <v>1.11</v>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>[21843.63, 14875.88, 17057.91]</t>
+          <t>[20136.99, 19185.58, 27208.84]</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>[25258.8, 18643.5, 15494.9]</t>
+          <t>[19826.1, 19147.2, 27639.0]</t>
         </is>
       </c>
     </row>
@@ -6222,31 +6222,31 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D161" t="n">
-        <v>4035.64</v>
+        <v>773.89</v>
       </c>
       <c r="E161" t="n">
-        <v>3065.97</v>
+        <v>546.71</v>
       </c>
       <c r="F161" t="n">
-        <v>20.16</v>
+        <v>2.11</v>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>[17301.75, 16577.0, 21405.76]</t>
+          <t>[19043.31, 26320.47, 21485.5]</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>[18643.5, 15494.9, 14631.7]</t>
+          <t>[19147.2, 27639.0, 21703.2]</t>
         </is>
       </c>
     </row>
@@ -6258,31 +6258,31 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D162" t="n">
-        <v>1971.18</v>
+        <v>3006.8</v>
       </c>
       <c r="E162" t="n">
-        <v>1668.49</v>
+        <v>2830.64</v>
       </c>
       <c r="F162" t="n">
-        <v>132.67</v>
+        <v>56.4</v>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>[4020.28, 3841.8, 3682.02]</t>
+          <t>[5438.93, 5474.84, 2185.1]</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>[932.7, 2505.8, 4263.9]</t>
+          <t>[7304.7, 3080.6, 6417.0]</t>
         </is>
       </c>
     </row>
@@ -6294,31 +6294,31 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D163" t="n">
-        <v>1925.41</v>
+        <v>3339.51</v>
       </c>
       <c r="E163" t="n">
-        <v>1619.5</v>
+        <v>3278.42</v>
       </c>
       <c r="F163" t="n">
-        <v>35.03</v>
+        <v>77.34999999999999</v>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>[2885.44, 2712.72, 2539.51]</t>
+          <t>[5943.09, 2240.19, 6572.25]</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>[2505.8, 4263.9, 5467.2]</t>
+          <t>[3080.6, 6417.0, 3776.3]</t>
         </is>
       </c>
     </row>
@@ -6330,31 +6330,31 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D164" t="n">
-        <v>3640.01</v>
+        <v>8228.85</v>
       </c>
       <c r="E164" t="n">
-        <v>3320.13</v>
+        <v>6713.82</v>
       </c>
       <c r="F164" t="n">
-        <v>54.69</v>
+        <v>110.33</v>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>[2609.57, 2435.97, 2278.97]</t>
+          <t>[2251.39, 6370.91, 20161.15]</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>[4263.9, 5467.2, 7553.8]</t>
+          <t>[6417.0, 3776.3, 6779.9]</t>
         </is>
       </c>
     </row>
@@ -6366,31 +6366,31 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D165" t="n">
-        <v>3913.17</v>
+        <v>7248.11</v>
       </c>
       <c r="E165" t="n">
-        <v>3800.26</v>
+        <v>4918.27</v>
       </c>
       <c r="F165" t="n">
-        <v>59.42</v>
+        <v>93.79000000000001</v>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>[2662.99, 2505.67, 2352.86]</t>
+          <t>[5675.46, 19181.19, 489.23]</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>[5467.2, 7553.8, 5901.3]</t>
+          <t>[3776.3, 6779.9, 943.6]</t>
         </is>
       </c>
     </row>
@@ -6402,31 +6402,31 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D166" t="n">
-        <v>5509.71</v>
+        <v>6785.26</v>
       </c>
       <c r="E166" t="n">
-        <v>5198.43</v>
+        <v>4271.66</v>
       </c>
       <c r="F166" t="n">
-        <v>64.17</v>
+        <v>82.48</v>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>[2821.09, 2669.38, 2530.34]</t>
+          <t>[18506.68, 469.22, 1922.98]</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>[7553.8, 5901.3, 10161.0]</t>
+          <t>[6779.9, 943.6, 2536.8]</t>
         </is>
       </c>
     </row>
@@ -6438,31 +6438,31 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D167" t="n">
-        <v>5092.98</v>
+        <v>394.12</v>
       </c>
       <c r="E167" t="n">
-        <v>4760.08</v>
+        <v>386.22</v>
       </c>
       <c r="F167" t="n">
-        <v>58.99</v>
+        <v>19.44</v>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>[3163.25, 3028.41, 2895.1]</t>
+          <t>[657.28, 2058.63, 3917.73]</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>[5901.3, 10161.0, 7304.7]</t>
+          <t>[943.6, 2536.8, 4311.9]</t>
         </is>
       </c>
     </row>
@@ -6474,31 +6474,31 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D168" t="n">
-        <v>4198.48</v>
+        <v>477.72</v>
       </c>
       <c r="E168" t="n">
-        <v>3626.33</v>
+        <v>428.06</v>
       </c>
       <c r="F168" t="n">
-        <v>49.01</v>
+        <v>13.42</v>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>[3803.58, 3985.0, 4282.46]</t>
+          <t>[1809.49, 4015.91, 5263.93]</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>[10161.0, 7304.7, 3080.6]</t>
+          <t>[2536.8, 4311.9, 5524.8]</t>
         </is>
       </c>
     </row>
@@ -6510,31 +6510,31 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D169" t="n">
-        <v>3006.8</v>
+        <v>104.78</v>
       </c>
       <c r="E169" t="n">
-        <v>2830.64</v>
+        <v>76.67</v>
       </c>
       <c r="F169" t="n">
-        <v>56.4</v>
+        <v>1.67</v>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>[5438.93, 5474.84, 2185.1]</t>
+          <t>[4137.17, 5476.19, 7612.97]</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>[7304.7, 3080.6, 6417.0]</t>
+          <t>[4311.9, 5524.8, 7606.3]</t>
         </is>
       </c>
     </row>
@@ -6546,31 +6546,31 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D170" t="n">
-        <v>3339.51</v>
+        <v>417.63</v>
       </c>
       <c r="E170" t="n">
-        <v>3278.42</v>
+        <v>274.35</v>
       </c>
       <c r="F170" t="n">
-        <v>77.34999999999999</v>
+        <v>4.59</v>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>[5943.09, 2240.19, 6572.25]</t>
+          <t>[5453.11, 7573.99, 6685.76]</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>[3080.6, 6417.0, 3776.3]</t>
+          <t>[5524.8, 7606.3, 5966.7]</t>
         </is>
       </c>
     </row>
@@ -6582,31 +6582,31 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D171" t="n">
-        <v>8228.85</v>
+        <v>561.5599999999999</v>
       </c>
       <c r="E171" t="n">
-        <v>6713.82</v>
+        <v>488.69</v>
       </c>
       <c r="F171" t="n">
-        <v>110.33</v>
+        <v>6.85</v>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>[2251.39, 6370.91, 20161.15]</t>
+          <t>[7741.65, 6777.55, 9522.63]</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>[6417.0, 3776.3, 6779.9]</t>
+          <t>[7606.3, 5966.7, 10042.5]</t>
         </is>
       </c>
     </row>
@@ -6618,31 +6618,31 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D172" t="n">
-        <v>4628.59</v>
+        <v>3630.05</v>
       </c>
       <c r="E172" t="n">
-        <v>4576.63</v>
+        <v>3513.23</v>
       </c>
       <c r="F172" t="n">
-        <v>31.8</v>
+        <v>17.18</v>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>[8124.94, 9132.19, 13219.47]</t>
+          <t>[22445.86, 16853.91, 14175.45]</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>[13562.1, 13681.1, 16963.3]</t>
+          <t>[24757.9, 20555.9, 18701.1]</t>
         </is>
       </c>
     </row>
@@ -6654,31 +6654,31 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D173" t="n">
-        <v>3694.38</v>
+        <v>4539.69</v>
       </c>
       <c r="E173" t="n">
-        <v>3642.72</v>
+        <v>4476.39</v>
       </c>
       <c r="F173" t="n">
-        <v>22.34</v>
+        <v>24.91</v>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>[9535.14, 14187.49, 15680.0]</t>
+          <t>[16970.93, 14288.92, 10687.96]</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>[13681.1, 16963.3, 19686.4]</t>
+          <t>[20555.9, 18701.1, 16120.0]</t>
         </is>
       </c>
     </row>
@@ -6690,31 +6690,31 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D174" t="n">
-        <v>2210.02</v>
+        <v>5340.99</v>
       </c>
       <c r="E174" t="n">
-        <v>2124.5</v>
+        <v>5256.16</v>
       </c>
       <c r="F174" t="n">
-        <v>10.94</v>
+        <v>30.55</v>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>[15156.49, 16709.97, 20977.23]</t>
+          <t>[14569.88, 10933.24, 10809.7]</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>[16963.3, 19686.4, 22567.5]</t>
+          <t>[18701.1, 16120.0, 17260.2]</t>
         </is>
       </c>
     </row>
@@ -6726,31 +6726,31 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D175" t="n">
-        <v>1819.44</v>
+        <v>6590.83</v>
       </c>
       <c r="E175" t="n">
-        <v>1512.22</v>
+        <v>6470.58</v>
       </c>
       <c r="F175" t="n">
-        <v>7.23</v>
+        <v>40.11</v>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>[16859.82, 21222.89, 26164.02]</t>
+          <t>[11075.1, 10988.71, 7266.16]</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>[19686.4, 22567.5, 26529.5]</t>
+          <t>[16120.0, 17260.2, 15361.5]</t>
         </is>
       </c>
     </row>
@@ -6762,31 +6762,31 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D176" t="n">
-        <v>1093.88</v>
+        <v>6811.37</v>
       </c>
       <c r="E176" t="n">
-        <v>913.34</v>
+        <v>6765.72</v>
       </c>
       <c r="F176" t="n">
-        <v>3.66</v>
+        <v>42.31</v>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>[21574.84, 26669.13, 24892.16]</t>
+          <t>[11255.49, 7511.59, 9258.75]</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>[22567.5, 26529.5, 26499.9]</t>
+          <t>[17260.2, 15361.5, 15701.3]</t>
         </is>
       </c>
     </row>
@@ -6798,31 +6798,31 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D177" t="n">
-        <v>1648.74</v>
+        <v>6497.97</v>
       </c>
       <c r="E177" t="n">
-        <v>1361.71</v>
+        <v>6449.14</v>
       </c>
       <c r="F177" t="n">
-        <v>5.34</v>
+        <v>39.27</v>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>[26638.26, 24856.27, 22425.15]</t>
+          <t>[7796.27, 9691.78, 13286.33]</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>[26529.5, 26499.9, 24757.9]</t>
+          <t>[15361.5, 15701.3, 19059.0]</t>
         </is>
       </c>
     </row>
@@ -6834,31 +6834,31 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D178" t="n">
-        <v>2806.18</v>
+        <v>5257.38</v>
       </c>
       <c r="E178" t="n">
-        <v>2669.66</v>
+        <v>5250.71</v>
       </c>
       <c r="F178" t="n">
-        <v>11.68</v>
+        <v>28.52</v>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>[24759.57, 22311.77, 16733.39]</t>
+          <t>[10173.56, 14164.73, 16265.16]</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>[26499.9, 24757.9, 20555.9]</t>
+          <t>[15701.3, 19059.0, 21595.3]</t>
         </is>
       </c>
     </row>
@@ -6870,31 +6870,31 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D179" t="n">
-        <v>3630.05</v>
+        <v>2933.87</v>
       </c>
       <c r="E179" t="n">
-        <v>3513.23</v>
+        <v>2574.89</v>
       </c>
       <c r="F179" t="n">
-        <v>17.18</v>
+        <v>12.56</v>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>[22445.86, 16853.91, 14175.45]</t>
+          <t>[15545.58, 17971.22, 23271.04]</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>[24757.9, 20555.9, 18701.1]</t>
+          <t>[19059.0, 21595.3, 23858.2]</t>
         </is>
       </c>
     </row>
@@ -6906,31 +6906,31 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D180" t="n">
-        <v>4539.69</v>
+        <v>1683.32</v>
       </c>
       <c r="E180" t="n">
-        <v>4476.39</v>
+        <v>1641.22</v>
       </c>
       <c r="F180" t="n">
-        <v>24.91</v>
+        <v>6.84</v>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>[16970.93, 14288.92, 10687.96]</t>
+          <t>[19427.45, 25279.9, 30805.82]</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>[20555.9, 18701.1, 16120.0]</t>
+          <t>[21595.3, 23858.2, 29471.7]</t>
         </is>
       </c>
     </row>
@@ -6942,31 +6942,31 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D181" t="n">
-        <v>5340.99</v>
+        <v>2902.18</v>
       </c>
       <c r="E181" t="n">
-        <v>5256.16</v>
+        <v>2899.47</v>
       </c>
       <c r="F181" t="n">
-        <v>30.55</v>
+        <v>10.69</v>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>[14569.88, 10933.24, 10809.7]</t>
+          <t>[26591.44, 32507.94, 31302.12]</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>[18701.1, 16120.0, 17260.2]</t>
+          <t>[23858.2, 29471.7, 28373.2]</t>
         </is>
       </c>
     </row>
@@ -6978,31 +6978,31 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D182" t="n">
-        <v>7793.66</v>
+        <v>3976.17</v>
       </c>
       <c r="E182" t="n">
-        <v>7777.19</v>
+        <v>3911.15</v>
       </c>
       <c r="F182" t="n">
-        <v>41.66</v>
+        <v>11.69</v>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>[9557.76, 10240.29, 13142.18]</t>
+          <t>[39090.1, 34863.08, 21595.46]</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>[16696.6, 18055.5, 21519.7]</t>
+          <t>[43225.3, 37806.9, 26249.9]</t>
         </is>
       </c>
     </row>
@@ -7014,31 +7014,31 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D183" t="n">
-        <v>6539.23</v>
+        <v>4883.99</v>
       </c>
       <c r="E183" t="n">
-        <v>6408.27</v>
+        <v>4596.58</v>
       </c>
       <c r="F183" t="n">
-        <v>29.42</v>
+        <v>18.91</v>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>[10736.79, 14180.42, 28978.38]</t>
+          <t>[35155.95, 21797.71, 13730.31]</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>[18055.5, 21519.7, 33545.2]</t>
+          <t>[37806.9, 26249.9, 20416.9]</t>
         </is>
       </c>
     </row>
@@ -7050,31 +7050,31 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D184" t="n">
-        <v>4038.07</v>
+        <v>6490.76</v>
       </c>
       <c r="E184" t="n">
-        <v>3620.62</v>
+        <v>6298.91</v>
       </c>
       <c r="F184" t="n">
-        <v>13.52</v>
+        <v>27.62</v>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>[15740.21, 32144.26, 34997.96]</t>
+          <t>[21981.33, 13870.15, 15326.09]</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>[21519.7, 33545.2, 38679.4]</t>
+          <t>[26249.9, 20416.9, 23407.5]</t>
         </is>
       </c>
     </row>
@@ -7086,31 +7086,31 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D185" t="n">
-        <v>2159.44</v>
+        <v>7835.5</v>
       </c>
       <c r="E185" t="n">
-        <v>1914.55</v>
+        <v>7764.31</v>
       </c>
       <c r="F185" t="n">
-        <v>4.66</v>
+        <v>38.5</v>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>[33042.21, 36105.4, 43122.54]</t>
+          <t>[13998.08, 15525.39, 8852.49]</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>[33545.2, 38679.4, 45789.2]</t>
+          <t>[20416.9, 23407.5, 17844.5]</t>
         </is>
       </c>
     </row>
@@ -7122,31 +7122,31 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D186" t="n">
-        <v>2488.21</v>
+        <v>8189.43</v>
       </c>
       <c r="E186" t="n">
-        <v>2472.94</v>
+        <v>8173.31</v>
       </c>
       <c r="F186" t="n">
-        <v>5.77</v>
+        <v>41.7</v>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>[36078.23, 43062.14, 43100.6]</t>
+          <t>[15913.71, 9109.56, 10490.4]</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>[38679.4, 45789.2, 45191.2]</t>
+          <t>[23407.5, 17844.5, 18781.6]</t>
         </is>
       </c>
     </row>
@@ -7158,31 +7158,31 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D187" t="n">
-        <v>3228.58</v>
+        <v>8344.65</v>
       </c>
       <c r="E187" t="n">
-        <v>3085.28</v>
+        <v>8338.08</v>
       </c>
       <c r="F187" t="n">
-        <v>6.95</v>
+        <v>42.38</v>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>[43003.87, 43091.59, 38854.39]</t>
+          <t>[9422.41, 10884.49, 14257.76]</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>[45789.2, 45191.2, 43225.3]</t>
+          <t>[17844.5, 18781.6, 22952.8]</t>
         </is>
       </c>
     </row>
@@ -7194,31 +7194,31 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D188" t="n">
-        <v>3204.78</v>
+        <v>6651.31</v>
       </c>
       <c r="E188" t="n">
-        <v>3064.74</v>
+        <v>6443.88</v>
       </c>
       <c r="F188" t="n">
-        <v>7.36</v>
+        <v>28.48</v>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>[43253.3, 38993.28, 34782.59]</t>
+          <t>[11374.9, 15152.08, 30216.07]</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>[45191.2, 43225.3, 37806.9]</t>
+          <t>[18781.6, 22952.8, 34340.3]</t>
         </is>
       </c>
     </row>
@@ -7230,31 +7230,31 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D189" t="n">
-        <v>3976.17</v>
+        <v>3571.83</v>
       </c>
       <c r="E189" t="n">
-        <v>3911.15</v>
+        <v>2368.29</v>
       </c>
       <c r="F189" t="n">
-        <v>11.69</v>
+        <v>9.81</v>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>[39090.1, 34863.08, 21595.46]</t>
+          <t>[16804.27, 33784.09, 39114.92]</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>[43225.3, 37806.9, 26249.9]</t>
+          <t>[22952.8, 34340.3, 38714.8]</t>
         </is>
       </c>
     </row>
@@ -7266,31 +7266,31 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D190" t="n">
-        <v>4883.99</v>
+        <v>3164.94</v>
       </c>
       <c r="E190" t="n">
-        <v>4596.58</v>
+        <v>2881.42</v>
       </c>
       <c r="F190" t="n">
-        <v>18.91</v>
+        <v>7.03</v>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>[35155.95, 21797.71, 13730.31]</t>
+          <t>[35701.42, 41440.98, 49758.46]</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>[37806.9, 26249.9, 20416.9]</t>
+          <t>[34340.3, 38714.8, 45201.5]</t>
         </is>
       </c>
     </row>
@@ -7302,31 +7302,31 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D191" t="n">
-        <v>6490.76</v>
+        <v>5972.86</v>
       </c>
       <c r="E191" t="n">
-        <v>6298.91</v>
+        <v>5888.57</v>
       </c>
       <c r="F191" t="n">
-        <v>27.62</v>
+        <v>13.44</v>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>[21981.33, 13870.15, 15326.09]</t>
+          <t>[43257.91, 52139.76, 52865.04]</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>[26249.9, 20416.9, 23407.5]</t>
+          <t>[38714.8, 45201.5, 46680.7]</t>
         </is>
       </c>
     </row>
@@ -7338,31 +7338,31 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D192" t="n">
-        <v>12531.92</v>
+        <v>2593.94</v>
       </c>
       <c r="E192" t="n">
-        <v>12440.1</v>
+        <v>1934.5</v>
       </c>
       <c r="F192" t="n">
-        <v>40.6</v>
+        <v>5.12</v>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>[15462.08, 17236.72, 22149.39]</t>
+          <t>[42954.92, 37179.56, 33197.22]</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>[26380.9, 29132.2, 36655.4]</t>
+          <t>[38641.4, 35950.3, 32936.5]</t>
         </is>
       </c>
     </row>
@@ -7374,31 +7374,31 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D193" t="n">
-        <v>12731.47</v>
+        <v>1277.98</v>
       </c>
       <c r="E193" t="n">
-        <v>12576.41</v>
+        <v>1178.88</v>
       </c>
       <c r="F193" t="n">
-        <v>34.88</v>
+        <v>3.55</v>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>[18439.43, 24932.98, 27279.95]</t>
+          <t>[37513.93, 33418.82, 32251.28]</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>[29132.2, 36655.4, 42594.0]</t>
+          <t>[35950.3, 32936.5, 30760.6]</t>
         </is>
       </c>
     </row>
@@ -7410,31 +7410,31 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D194" t="n">
-        <v>12613.37</v>
+        <v>1898.32</v>
       </c>
       <c r="E194" t="n">
-        <v>12250.34</v>
+        <v>1573.58</v>
       </c>
       <c r="F194" t="n">
-        <v>27.81</v>
+        <v>5.33</v>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>[27908.0, 30674.58, 34865.29]</t>
+          <t>[33322.84, 32131.55, 31580.27]</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>[36655.4, 42594.0, 50949.5]</t>
+          <t>[32936.5, 30760.6, 28616.8]</t>
         </is>
       </c>
     </row>
@@ -7446,31 +7446,31 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D195" t="n">
-        <v>11115.07</v>
+        <v>3997.56</v>
       </c>
       <c r="E195" t="n">
-        <v>10856.63</v>
+        <v>3319.38</v>
       </c>
       <c r="F195" t="n">
-        <v>21.69</v>
+        <v>10.51</v>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>[34644.6, 40115.28, 41037.93]</t>
+          <t>[31744.72, 31272.62, 26839.8]</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>[42594.0, 50949.5, 54824.2]</t>
+          <t>[30760.6, 28616.8, 33158.0]</t>
         </is>
       </c>
     </row>
@@ -7482,31 +7482,31 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D196" t="n">
-        <v>9207.450000000001</v>
+        <v>5257.75</v>
       </c>
       <c r="E196" t="n">
-        <v>8330.74</v>
+        <v>4996.98</v>
       </c>
       <c r="F196" t="n">
-        <v>16.34</v>
+        <v>15.08</v>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>[41291.78, 42493.99, 36639.02]</t>
+          <t>[31308.33, 26850.96, 29631.33]</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>[50949.5, 54824.2, 39643.3]</t>
+          <t>[28616.8, 33158.0, 35623.7]</t>
         </is>
       </c>
     </row>
@@ -7518,31 +7518,31 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D197" t="n">
-        <v>3662.43</v>
+        <v>6292.05</v>
       </c>
       <c r="E197" t="n">
-        <v>3482.97</v>
+        <v>6221.38</v>
       </c>
       <c r="F197" t="n">
-        <v>8.140000000000001</v>
+        <v>17.06</v>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>[51822.94, 44689.8, 41042.55]</t>
+          <t>[26366.21, 28647.13, 39190.62]</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>[54824.2, 39643.3, 38641.4]</t>
+          <t>[33158.0, 35623.7, 44086.4]</t>
         </is>
       </c>
     </row>
@@ -7554,31 +7554,31 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D198" t="n">
-        <v>5152.59</v>
+        <v>4157.39</v>
       </c>
       <c r="E198" t="n">
-        <v>4542.46</v>
+        <v>3819.27</v>
       </c>
       <c r="F198" t="n">
-        <v>11.69</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>[47145.69, 43221.08, 37495.62]</t>
+          <t>[29776.84, 40299.97, 48165.98]</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>[39643.3, 38641.4, 35950.3]</t>
+          <t>[35623.7, 44086.4, 49990.5]</t>
         </is>
       </c>
     </row>
@@ -7590,31 +7590,31 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D199" t="n">
-        <v>2593.94</v>
+        <v>1841.52</v>
       </c>
       <c r="E199" t="n">
-        <v>1934.5</v>
+        <v>1404.17</v>
       </c>
       <c r="F199" t="n">
-        <v>5.12</v>
+        <v>3.05</v>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>[42954.92, 37179.56, 33197.22]</t>
+          <t>[41023.63, 49158.7, 59621.03]</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>[38641.4, 35950.3, 32936.5]</t>
+          <t>[44086.4, 49990.5, 59303.1]</t>
         </is>
       </c>
     </row>
@@ -7626,31 +7626,31 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D200" t="n">
-        <v>1277.98</v>
+        <v>2608.11</v>
       </c>
       <c r="E200" t="n">
-        <v>1178.88</v>
+        <v>2173.7</v>
       </c>
       <c r="F200" t="n">
-        <v>3.55</v>
+        <v>3.62</v>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>[37513.93, 33418.82, 32251.28]</t>
+          <t>[50315.24, 61658.36, 65543.98]</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>[35950.3, 32936.5, 30760.6]</t>
+          <t>[49990.5, 59303.1, 61702.9]</t>
         </is>
       </c>
     </row>
@@ -7662,31 +7662,31 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D201" t="n">
-        <v>1898.32</v>
+        <v>5428.98</v>
       </c>
       <c r="E201" t="n">
-        <v>1573.58</v>
+        <v>4570.09</v>
       </c>
       <c r="F201" t="n">
-        <v>5.33</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>[33322.84, 32131.55, 31580.27]</t>
+          <t>[61037.05, 65073.93, 52100.79]</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>[32936.5, 30760.6, 28616.8]</t>
+          <t>[59303.1, 61702.9, 43495.5]</t>
         </is>
       </c>
     </row>
